--- a/data_extactor/batch/751_800.xlsx
+++ b/data_extactor/batch/751_800.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B58441-67C8-42B8-935A-8351444F4B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1630 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="539">
+  <si>
+    <t>47-4011.00</t>
+  </si>
+  <si>
+    <t>Construction and Building Inspectors</t>
+  </si>
+  <si>
+    <t>Building Code Administrator | Building Inspector | Building Official | Code Enforcement Officer | Code Inspector | Combination Building Inspector | Construction Inspector | Electrical Inspector | Plumbing Inspector | Public Works Inspector</t>
+  </si>
+  <si>
+    <t>Arc Second PocketCAD | Autodesk AutoCAD | Automated permit system software | Database software | ESRI ArcView | Email software | Inspection Depot Home Guide System | Intuit QuickBooks | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Mobile building inspection software | Municipal geographic management software | New construction inspection form software | NorthWest Builders Network Plan Analyst | OptaSoft Commercial Building Inspector | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | Quicken | Real estate and tax software | Residential home inspection form software | SAP software | Trimble Digital Fieldbook | Vision Software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Active Learning | Monitoring | Learning Strategies | Mathematics</t>
+  </si>
+  <si>
+    <t>Building and Construction | Public Safety and Security | English Language | Customer and Personal Service | Design | Law and Government | Mathematics | Administration and Management | Mechanical | Administrative | Computers and Electronics | Engineering and Technology | Education and Training</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Written Comprehension | Oral Expression | Inductive Reasoning | Deductive Reasoning | Oral Comprehension | Written Expression | Near Vision | Speech Recognition | Speech Clarity | Information Ordering | Far Vision | Selective Attention | Flexibility of Closure | Category Flexibility | Visual Color Discrimination | Visualization | Perceptual Speed | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Time Pressure | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Outdoors, Under Cover | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Architects, Except Landscape and Naval | Aviation Inspectors | Civil Engineering Technologists and Technicians | Civil Engineers | Construction Managers | Electricians | Energy Auditors | Environmental Compliance Inspectors | Fire-Prevention and Protection Engineers | First-Line Supervisors of Construction Trades and Extraction Workers | Government Property Inspectors and Investigators | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Industrial Engineers | Inspectors, Testers, Sorters, Samplers, and Weighers | Maintenance and Repair Workers, General | Occupational Health and Safety Specialists | Plumbers, Pipefitters, and Steamfitters | Solar Energy Installation Managers | Transportation Inspectors | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Inspect structures using engineering skills to determine structural soundness and compliance with specifications, building codes, and other regulations. Inspections may be general in nature or may be limited to a specific area, such as electrical systems or plumbing.</t>
+  </si>
+  <si>
+    <t>Approve building plans that meet required specifications. | Conduct environmental hazard inspections to identify or quantify problems, such as asbestos, poor air quality, water contamination, or other environmental hazards. | Conduct inspections, using survey instruments, metering devices, tape measures, or test equipment. | Confer with owners, violators, or authorities to explain regulations or recommend remedial actions. | Estimate cost of completed work or of needed renovations or upgrades. | Evaluate premises for cleanliness, such as proper garbage disposal or lack of vermin infestation. | Evaluate project details to ensure adherence to environmental regulations. | Examine lifting or conveying devices, such as elevators, escalators, moving sidewalks, hoists, inclined railways, ski lifts, or amusement rides to ensure safety and proper functioning. | Inspect and monitor construction sites to ensure adherence to safety standards, building codes, or specifications. | Inspect bridges, dams, highways, buildings, wiring, plumbing, electrical circuits, sewers, heating systems, or foundations during and after construction for structural quality, general safety, or conformance to specifications and codes. | Inspect facilities or installations to determine their environmental impact. | Issue permits for construction, relocation, demolition, or occupancy. | Maintain daily logs and supplement inspection records with photographs. | Measure dimensions and verify level, alignment, or elevation of structures or fixtures to ensure compliance to building plans and codes. | Monitor construction activities to ensure that environmental regulations are not violated. | Monitor installation of plumbing, wiring, equipment, or appliances to ensure that installation is performed properly and is in compliance with applicable regulations. | Review and interpret plans, blueprints, site layouts, specifications, or construction methods to ensure compliance to legal requirements and safety regulations. | Sample and test air to identify gasses, such as bromine, ozone, or sulfur dioxide, or particulates, such as mold, dust, or allergens. | Train, direct, or supervise other construction inspectors.</t>
+  </si>
+  <si>
+    <t>47-4011.01</t>
+  </si>
+  <si>
+    <t>Energy Auditors</t>
+  </si>
+  <si>
+    <t>Building Performance Consultant | Building Science and Energy Specialist | Building Scientist | Energy Advisor | Energy Auditor | Energy Consultant | Energy Rater | Energy and Building Systems Specialist | Home Energy Inspector | Home Performance Consultant</t>
+  </si>
+  <si>
+    <t>ACCA Manual J | Abraxas Energy Consulting Metrix | Adobe Photoshop | Architectural Energy Corporation ENFORMA Building Diagnostics | Architectural Energy Corporation REM/Rate | Autodesk AutoCAD | C++ | Cool Roof Calculator | DesignBuilder Software DesignBuilder | EffTec EffTrack | Ekotrope RATER | Elite Software Energy Audit | Enercom Energy Depot for Business | Enercom Energy Depot for Homes | Energy Efficient Rehab Advisor | EnergyPlus | Esri ArcGIS | Facility Energy Decision Systems FEDS | Federal Renewable Energy Screening Assistant FRESA | Fielding Data Labs OptoMizer | Fundamental Objects foAudits | Good Steward Software EnergyCAP | Home Energy Efficient Design HEED | IBM SPSS Statistics | InterEnergy Software Building Energy Analyzer PRO | Itron Enterprise Energy Management EEM Suite | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual FoxPro | Microsoft Word | MotorMaster+ | Onset Computer Corporation HOBOware | Performance Systems Development TREAT | Program for Energy Analysis of Residences PEAR | Psychrometric chart software | Python | R | REScheck | Retrofit Energy Savings Estimation Model RESEM | SAP software | SAS | Salesforce software | Snugg Home Snugg Pro | Structured query language SQL | The MathWorks MATLAB | The Weatherization Assistant | Trane TRACE | UNIX | Web browser software | Wolfram Research Mathematica | dBASE</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Speaking | Active Listening | Critical Thinking | Writing | Mathematics | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Building and Construction | Mathematics | Engineering and Technology | Mechanical | Physics | English Language | Sales and Marketing | Design | Computers and Electronics | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Mathematical Reasoning | Near Vision | Number Facility | Information Ordering | Fluency of Ideas | Flexibility of Closure | Speech Recognition | Speech Clarity | Category Flexibility | Visualization | Perceptual Speed | Speed of Closure | Originality | Far Vision | Control Precision</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Frequency of Decision Making | Time Pressure | Contact With Others | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General | Outdoors, Exposed to All Weather Conditions | Indoors, Environmentally Controlled | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Biofuels/Biodiesel Technology and Product Development Managers | Biomass Power Plant Managers | Construction and Building Inspectors | Energy Engineers, Except Wind and Solar | Environmental Engineering Technologists and Technicians | Geothermal Production Managers | Industrial Ecologists | Industrial Engineering Technologists and Technicians | Industrial Engineers | Power Distributors and Dispatchers | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Solar Sales Representatives and Assessors | Sustainability Specialists | Water/Wastewater Engineers | Weatherization Installers and Technicians | Wind Energy Development Managers | Wind Energy Engineers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Conduct energy audits of buildings, building systems, or process systems. May also conduct investment grade audits of buildings or systems.</t>
+  </si>
+  <si>
+    <t>Analyze energy bills, including utility rates or tariffs, to gather historical energy usage data. | Analyze technical feasibility of energy-saving measures, using knowledge of engineering, energy production, energy use, construction, maintenance, system operation, or process systems. | Calculate potential for energy savings. | Collect and analyze field data related to energy usage. | Compare existing energy consumption levels to normative data. | Determine patterns of building use to show annual or monthly needs for heating, cooling, lighting, or other energy needs. | Educate customers on energy efficiency or answer questions on topics such as the costs of running household appliances or the selection of energy-efficient appliances. | Examine commercial sites to determine the feasibility of installing equipment that allows building management systems to reduce electricity consumption during peak demand periods. | Identify and prioritize energy-saving measures. | Identify any health or safety issues related to planned weatherization projects. | Identify opportunities to improve the operation, maintenance, or energy efficiency of building or process systems. | Inspect newly installed energy-efficient equipment to ensure that it was installed properly and is performing according to specifications. | Inspect or evaluate building envelopes, mechanical systems, electrical systems, or process systems to determine the energy consumption of each system. | Measure energy usage with devices such as data loggers, universal data recorders, light meters, sling psychrometers, psychrometric charts, flue gas analyzers, amp probes, watt meters, volt meters, thermometers, or utility meters. | Oversee installation of equipment such as water heater wraps, pipe insulation, weatherstripping, door sweeps, or low-flow showerheads to improve energy efficiency. | Perform tests such as blower-door tests to locate air leaks. | Prepare audit reports containing energy analysis results or recommendations for energy cost savings. | Prepare job specification sheets for home energy improvements, such as attic insulation, window retrofits, or heating system upgrades. | Quantify energy consumption to establish baselines for energy use or need. | Recommend energy-efficient technologies or alternate energy sources. | Verify income eligibility of participants in publicly financed weatherization programs.</t>
+  </si>
+  <si>
+    <t>47-4021.00</t>
+  </si>
+  <si>
+    <t>Elevator and Escalator Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Elevator Adjuster | Elevator Constructor | Elevator Installer | Elevator Mechanic | Elevator Repair and Maintenance Technician (Elevator Repair and Maintenance Tech) | Elevator Service Mechanic | Elevator Service Technician (Elevator Service Tech) | Elevator Serviceman | Elevator Technician (Elevator Tech) | Elevator Troubleshooter</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Elevator Controls INTERACT | Microsoft Excel | Microsoft Outlook | Microsoft Word | Scheduling software | Troubleshooting software | WORLD Electronics Freedomware</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Active Learning | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Building and Construction | Public Safety and Security | Computers and Electronics | Mathematics | Engineering and Technology | English Language | Administration and Management</t>
+  </si>
+  <si>
+    <t>Deductive Reasoning | Problem Sensitivity | Manual Dexterity | Oral Comprehension | Near Vision | Finger Dexterity | Arm-Hand Steadiness | Inductive Reasoning | Information Ordering | Extent Flexibility | Visualization | Control Precision | Oral Expression | Written Expression | Written Comprehension | Gross Body Equilibrium | Trunk Strength | Reaction Time | Multilimb Coordination | Flexibility of Closure | Category Flexibility | Speech Recognition | Selective Attention</t>
+  </si>
+  <si>
+    <t>Frequency of Decision Making | Exposed to Hazardous Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | E-Mail | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Exposed to High Places | Exposed to Cramped Work Space, Awkward Positions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Bending or Twisting Your Body | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Environmentally Controlled | Deal With External Customers or the Public in General | Contact With Others | Exposed to Hazardous Equipment | Consequence of Error | Exposed to Contaminants | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Time Pressure | Spend Time Standing | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Work With or Contribute to a Work Group or Team | Level of Competition | Importance of Repeating Same Tasks | Physical Proximity | Spend Time Walking or Running | Spend Time Making Repetitive Motions | Spend Time Kneeling, Crouching, Stooping, or Crawling</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Engine and Other Machine Assemblers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Installation, Maintenance, and Repair Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Maintenance and Repair Workers, General | Mechanical Door Repairers | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Plumbers, Pipefitters, and Steamfitters | Rail Car Repairers | Riggers | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Assemble, install, repair, or maintain electric or hydraulic freight or passenger elevators, escalators, or dumbwaiters.</t>
+  </si>
+  <si>
+    <t>Adjust safety controls, counterweights, door mechanisms, and components such as valves, ratchets, seals, and brake linings. | Assemble electrically powered stairs, steel frameworks, and tracks, and install associated motors and electrical wiring. | Assemble elevator cars, installing each car's platform, walls, and doors. | Assemble, install, repair, and maintain elevators, escalators, moving sidewalks, and dumbwaiters, using hand and power tools, and testing devices such as test lamps, ammeters, and voltmeters. | Attach guide shoes and rollers to minimize the lateral motion of cars as they travel through shafts. | Bolt or weld steel rails to the walls of shafts to guide elevators, working from scaffolding or platforms. | Check that safety regulations and building codes are met, and complete service reports verifying conformance to standards. | Connect car frames to counterweights, using steel cables. | Connect electrical wiring to control panels and electric motors. | Cut prefabricated sections of framework, rails, and other components to specified dimensions. | Disassemble defective units, and repair or replace parts such as locks, gears, cables, and electric wiring. | Inspect wiring connections, control panel hookups, door installations, and alignments and clearances of cars and hoistways to ensure that equipment will operate properly. | Install electrical wires and controls by attaching conduit along shaft walls from floor to floor and pulling plastic-covered wires through the conduit. | Install outer doors and door frames at elevator entrances on each floor of a structure. | Locate malfunctions in brakes, motors, switches, and signal and control systems, using test equipment. | Maintain log books that detail all repairs and checks performed. | Operate elevators to determine power demands, and test power consumption to detect overload factors. | Participate in additional training to keep skills up to date. | Read and interpret blueprints to determine the layout of system components, frameworks, and foundations, and to select installation equipment. | Test newly installed equipment to ensure that it meets specifications, such as stopping at floors for set amounts of time.</t>
+  </si>
+  <si>
+    <t>47-4031.00</t>
+  </si>
+  <si>
+    <t>Fence Erectors</t>
+  </si>
+  <si>
+    <t>Fence Builder | Fence Contractor | Fence Erector | Fence Installer | Fence Laborer | Fence Mechanic | Fence Technician (Fence Tech) | Gate Technician (Gate Tech) | Wood Fence Erector</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Cutlist Plus fx | Facebook | Maxwell Systems American Contractor | Microsoft Excel | Software Design Associates Computer Fencing System CFS</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Building and Construction | Transportation | Administration and Management | Design | Mathematics | English Language | Education and Training | Mechanical | Sales and Marketing | Production and Processing | Engineering and Technology | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Manual Dexterity | Multilimb Coordination | Static Strength | Arm-Hand Steadiness | Finger Dexterity | Control Precision | Information Ordering | Near Vision | Stamina | Dynamic Strength | Speech Recognition | Depth Perception | Extent Flexibility | Reaction Time | Deductive Reasoning | Problem Sensitivity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Work Outcomes and Results of Other Workers | Time Pressure | Determine Tasks, Priorities and Goals | Spend Time Standing | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Exposed to Hazardous Equipment | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Consequence of Error | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Walking or Running | Spend Time Bending or Twisting Your Body | Physical Proximity | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to High Places | Exposed to Very Hot or Cold Temperatures | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | In an Open Vehicle or Operating Equipment | Deal With External Customers or the Public in General | Spend Time Kneeling, Crouching, Stooping, or Crawling</t>
+  </si>
+  <si>
+    <t>Carpenters | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Electrical Power-Line Installers and Repairers | Electricians | Helpers--Carpenters | Helpers--Electricians | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Layout Workers, Metal and Plastic | Mechanical Door Repairers | Pipelayers | Rail-Track Laying and Maintenance Equipment Operators | Reinforcing Iron and Rebar Workers | Roofers | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters</t>
+  </si>
+  <si>
+    <t>Erect and repair fences and fence gates, using hand and power tools.</t>
+  </si>
+  <si>
+    <t>Align posts, by lines or sighting, and verify vertical alignment of posts, using plumb bobs or spirit levels. | Assemble gates, and fasten gates into position, using hand tools. | Attach fence rail supports to posts, using hammers and pliers. | Attach rails or tension wire along bottoms of posts to form fencing frames. | Blast rock formations and rocky areas with dynamite to facilitate posthole digging. | Complete top fence rails of metal fences by connecting tube sections, using metal sleeves. | Construct and repair barriers, retaining walls, trellises, and other types of fences, walls, and gates. | Dig postholes, using spades, posthole diggers, or power-driven augers. | Discuss fencing needs with customers, and estimate and quote prices. | Erect alternate panel, basket weave, and louvered fences. | Establish the location for a fence, and gather information needed to ensure that there are no electric cables or water lines in the area. | Insert metal tubing through rail supports. | Make rails for fences, by sawing lumber or by cutting metal tubing to required lengths. | Measure and lay out fence lines and mark posthole positions, following instructions, drawings, or specifications. | Mix and pour concrete around bases of posts, or tamp soil into postholes to embed posts. | Nail pointed slats to rails to construct picket fences. | Nail top and bottom rails to fence posts, or insert them in slots on posts. | Set metal or wooden posts in upright positions in postholes. | Stretch wire, wire mesh, or chain link fencing between posts, and attach fencing to frames. | Weld metal parts together, using portable gas welding equipment.</t>
+  </si>
+  <si>
+    <t>47-4041.00</t>
+  </si>
+  <si>
+    <t>Hazardous Materials Removal Workers</t>
+  </si>
+  <si>
+    <t>Abatement Worker | Asbestos Abatement Worker | Asbestos Hazard Abatement Worker | Asbestos Remover | Asbestos Worker | Decontamination and Decommissioning Operator (D and D Operator) | Hazmat Technician (Hazardous Materials Technician) | Waste Handling Technician</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system software CMMS | Database software | Inventory management systems | Jenkins CI | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | Xactware Xactimate</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension | Speaking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management | Transportation | Customer and Personal Service | Building and Construction | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Control Precision | Near Vision | Oral Expression | Speech Recognition | Arm-Hand Steadiness | Category Flexibility | Deductive Reasoning | Written Expression | Multilimb Coordination | Information Ordering | Inductive Reasoning | Visualization | Manual Dexterity | Speech Clarity | Written Comprehension | Extent Flexibility | Selective Attention | Far Vision | Static Strength | Finger Dexterity | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Health and Safety of Other Workers | Exposed to Contaminants | Telephone Conversations | Work With or Contribute to a Work Group or Team | Contact With Others | Time Pressure | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Indoors, Not Environmentally Controlled | Physical Proximity | Spend Time Walking or Running | Outdoors, Exposed to All Weather Conditions | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Chemical Plant and System Operators | Cleaners of Vehicles and Equipment | Construction Laborers | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Science and Protection Technicians, Including Health | Explosives Workers, Ordnance Handling Experts, and Blasters | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Helpers--Extraction Workers | Highway Maintenance Workers | Insulation Workers, Floor, Ceiling, and Wall | Maintenance and Repair Workers, General | Nuclear Monitoring Technicians | Occupational Health and Safety Specialists | Operating Engineers and Other Construction Equipment Operators | Recycling Coordinators | Recycling and Reclamation Workers | Refuse and Recyclable Material Collectors | Septic Tank Servicers and Sewer Pipe Cleaners | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Identify, remove, pack, transport, or dispose of hazardous materials, including asbestos, lead-based paint, waste oil, fuel, transmission fluid, radioactive materials, or contaminated soil. Specialized training and certification in hazardous materials handling or a confined entry permit are generally required. May operate earth-moving equipment or trucks.</t>
+  </si>
+  <si>
+    <t>Apply bioremediation techniques to hazardous wastes to allow naturally occurring bacteria to break down toxic substances. | Build containment areas prior to beginning abatement or decontamination work. | Clean contaminated equipment or areas for reuse, using detergents or solvents, sandblasters, filter pumps, or steam cleaners. | Clean mold-contaminated sites by removing damaged porous materials or thoroughly cleaning all contaminated nonporous materials. | Comply with prescribed safety procedures or federal laws regulating waste disposal methods. | Drive trucks or other heavy equipment to convey contaminated waste to designated sea or ground locations. | Identify asbestos, lead, or other hazardous materials to be removed, using monitoring devices. | Identify or separate waste products or materials for recycling or reuse. | Load or unload materials into containers or onto trucks, using hoists or forklifts. | Mix or pour concrete into forms to encase waste material for disposal. | Operate cranes to move or load baskets, casks, or canisters. | Operate machines or equipment to remove, package, store, or transport loads of waste materials. | Organize or track the locations of hazardous items in landfills. | Package, store, or move irradiated fuel elements in the underwater storage basins of nuclear reactor plants, using machines or equipment. | Prepare hazardous material for removal or storage. | Process e-waste, such as computer components containing lead or mercury. | Record numbers of containers stored at disposal sites, specifying amounts or types of equipment or waste disposed. | Remove asbestos or lead from surfaces, using hand or power tools such as scrapers, vacuums, or high-pressure sprayers. | Remove or limit contamination following emergencies involving hazardous substances. | Sort specialized hazardous waste at landfills or disposal centers, following proper disposal procedures. | Upload baskets of irradiated elements onto machines that insert fuel elements into canisters and secure lids.</t>
+  </si>
+  <si>
+    <t>47-4051.00</t>
+  </si>
+  <si>
+    <t>Highway Maintenance Workers</t>
+  </si>
+  <si>
+    <t>Equipment Operator (EO) | Highway Maintainer | Highway Maintenance Crew Worker | Highway Maintenance Technician | Highway Maintenance Worker | Maintenance Technician | Maintenance Worker | Transportation Maintenance Operator | Transportation Maintenance Specialist (TMS) | Transportation Worker</t>
+  </si>
+  <si>
+    <t>Database software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | English Language | Transportation | Building and Construction | Education and Training | Administration and Management</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Arm-Hand Steadiness | Problem Sensitivity | Oral Comprehension | Static Strength | Near Vision | Auditory Attention | Manual Dexterity | Information Ordering | Oral Expression | Selective Attention | Visualization | Flexibility of Closure | Far Vision | Extent Flexibility | Stamina | Trunk Strength | Reaction Time | Response Orientation | Finger Dexterity | Speech Clarity | Speech Recognition | Depth Perception | Rate Control | Time Sharing | Perceptual Speed | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Hazardous Equipment | Contact With Others | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Spend Time Making Repetitive Motions | Consequence of Error | Spend Time Bending or Twisting Your Body | Importance of Being Exact or Accurate | Exposed to Whole Body Vibration | Health and Safety of Other Workers | Spend Time Standing | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Physical Proximity | Time Pressure | Conflict Situations | In an Open Vehicle or Operating Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Extremely Bright or Inadequate Lighting Conditions | Indoors, Not Environmentally Controlled | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Construction Laborers | Electrical Power-Line Installers and Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Hazardous Materials Removal Workers | Heavy and Tractor-Trailer Truck Drivers | Helpers--Electricians | Helpers--Extraction Workers | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Maintenance and Repair Workers, General | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Rail Car Repairers | Rail-Track Laying and Maintenance Equipment Operators | Septic Tank Servicers and Sewer Pipe Cleaners | Traffic Technicians | Transportation Engineers | Transportation Vehicle, Equipment and Systems Inspectors, Except Aviation</t>
+  </si>
+  <si>
+    <t>Maintain highways, municipal and rural roads, airport runways, and rights-of-way. Duties include patching broken or eroded pavement and repairing guard rails, highway markers, and snow fences. May also mow or clear brush from along road, or plow snow from roadway.</t>
+  </si>
+  <si>
+    <t>Apply oil to road surfaces, using sprayers. | Apply poisons along roadsides and in animal burrows to eliminate unwanted roadside vegetation and rodents. | Blend compounds to form adhesive mixtures used for marker installation. | Clean and clear debris from culverts, catch basins, drop inlets, ditches, and other drain structures. | Drive heavy equipment and vehicles with adjustable attachments to sweep debris from paved surfaces, mow grass and weeds, remove snow and ice, and spread salt and sand. | Drive trucks to transport crews and equipment to work sites. | Dump, spread, and tamp asphalt, using pneumatic tampers, to repair joints and patch broken pavement. | Erect, install, or repair guardrails, road shoulders, berms, highway markers, warning signals, and highway lighting, using hand tools and power tools. | Flag motorists to warn them of obstacles or repair work ahead. | Haul and spread sand, gravel, and clay to fill washouts and repair road shoulders. | Inspect markers to verify accurate installation. | Inspect, clean, and repair drainage systems, bridges, tunnels, and other structures. | Measure and mark locations for installation of markers, using tape, string, or chalk. | Paint traffic control lines and place pavement traffic messages, by hand or using machines. | Perform preventative maintenance on vehicles and heavy equipment. | Perform roadside landscaping work, such as clearing weeds and brush, and planting and trimming trees. | Place and remove snow fences used to prevent the accumulation of drifting snow on highways. | Remove litter and debris from roadways, including debris from rock and mud slides. | Set out signs and cones around work areas to divert traffic.</t>
+  </si>
+  <si>
+    <t>47-4061.00</t>
+  </si>
+  <si>
+    <t>Rail-Track Laying and Maintenance Equipment Operators</t>
+  </si>
+  <si>
+    <t>Machine Operator | Rail Maintenance Worker | Track Equipment Operator (TEO) | Track Inspector | Track Laborer | Track Maintainer | Track Repairer | Track Walker | Trackman</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Timekeeping software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Transportation | Mechanical | Building and Construction | Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Control Precision | Manual Dexterity | Multilimb Coordination | Arm-Hand Steadiness | Reaction Time | Far Vision | Problem Sensitivity | Flexibility of Closure | Depth Perception | Near Vision | Visualization | Perceptual Speed | Rate Control | Static Strength | Oral Comprehension | Auditory Attention | Extent Flexibility | Trunk Strength | Dynamic Strength | Response Orientation | Finger Dexterity | Selective Attention | Information Ordering | Deductive Reasoning | Hearing Sensitivity | Gross Body Coordination | Stamina | Inductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Telephone Conversations | Physical Proximity | Health and Safety of Other Workers | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Exposed to Contaminants | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Time Pressure | Exposed to Minor Burns, Cuts, Bites, or Stings | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Spend Time Bending or Twisting Your Body | Exposed to Whole Body Vibration | Pace Determined by Speed of Equipment | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Construction Laborers | Continuous Mining Machine Operators | Earth Drillers, Except Oil and Gas | Electric Motor, Power Tool, and Related Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Highway Maintenance Workers | Hoist and Winch Operators | Loading and Moving Machine Operators, Underground Mining | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Pipelayers | Rail Car Repairers | Riggers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Lay, repair, and maintain track for standard or narrow-gauge railroad equipment used in regular railroad service or in plant yards, quarries, sand and gravel pits, and mines. Includes ballast cleaning machine operators and railroad bed tamping machine operators.</t>
+  </si>
+  <si>
+    <t>Adjust controls of machines that spread, shape, raise, level, or align track, according to specifications. | Clean or make minor repairs to machines or equipment. | Clean tracks or clear ice or snow from tracks or switch boxes. | Clean, grade, or level ballast on railroad tracks. | Cut rails to specified lengths, using rail saws. | Dress and reshape worn or damaged railroad switch points or frogs, using portable power grinders. | Drill holes through rails, tie plates, or fishplates for insertion of bolts or spikes, using power drills. | Drive graders, tamping machines, brooms, or ballast spreading machines to redistribute gravel or ballast between rails. | Drive vehicles that automatically move and lay tracks or rails over sections of track to be constructed, repaired, or maintained. | Engage mechanisms that lay tracks or rails to specified gauges. | Grind ends of new or worn rails to attain smooth joints, using portable grinders. | Lubricate machines, change oil, or fill hydraulic reservoirs to specified levels. | Observe leveling indicator arms to verify levelness and alignment of tracks. | Operate single- or multiple-head spike driving machines to drive spikes into ties and secure rails. | Operate single- or multiple-head spike pullers to pull old spikes from ties. | Operate tie-adzing machines to cut ties and permit insertion of fishplates that hold rails. | Operate track wrenches to tighten or loosen bolts at joints that hold ends of rails together. | Paint railroad signs, such as speed limits or gate-crossing warnings. | Patrol assigned track sections so that damaged or broken track can be located and reported. | Push controls to close grasping devices on track or rail sections so that they can be raised or moved. | Raise rails, using hydraulic jacks, to allow for tie removal and replacement. | Repair or adjust track switches, using wrenches and replacement parts. | Spray ties, fishplates, or joints with oil to protect them from weathering. | String and attach wire-guidelines machine to rails so that tracks or rails can be aligned or leveled. | Turn wheels of machines, using lever controls, to adjust guidelines for track alignments or grades, following specifications. | Weld sections of track together, such as switch points and frogs.</t>
+  </si>
+  <si>
+    <t>47-4071.00</t>
+  </si>
+  <si>
+    <t>Septic Tank Servicers and Sewer Pipe Cleaners</t>
+  </si>
+  <si>
+    <t>Drain Cleaner | Drain Technician | Public Works Technician | Septic Cleaner | Septic Pump Truck Driver | Septic Tank Service Technician | Service Technician | Sewer Bricklayer</t>
+  </si>
+  <si>
+    <t>Intuit QuickBooks | Microsoft Excel | Microsoft Word | Route mapping software | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Transportation | Mechanical | English Language | Public Safety and Security | Mathematics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Control Precision | Multilimb Coordination | Arm-Hand Steadiness | Flexibility of Closure | Problem Sensitivity | Oral Comprehension | Depth Perception | Reaction Time | Near Vision | Hearing Sensitivity | Deductive Reasoning | Oral Expression | Far Vision | Extent Flexibility | Static Strength | Auditory Attention | Trunk Strength | Selective Attention | Visualization | Perceptual Speed | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Freedom to Make Decisions | Health and Safety of Other Workers | Time Pressure | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Exposed to Hazardous Equipment | Work Outcomes and Results of Other Workers | Spend Time Bending or Twisting Your Body | In an Open Vehicle or Operating Equipment | Exposed to Disease or Infections | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Cleaners of Vehicles and Equipment | Construction Laborers | Control and Valve Installers and Repairers, Except Mechanical Door | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Hazardous Materials Removal Workers | Helpers--Extraction Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Highway Maintenance Workers | Maintenance and Repair Workers, General | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Pump Operators, Except Wellhead Pumpers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Clean and repair septic tanks, sewer lines, or drains. May patch walls and partitions of tank, replace damaged drain tile, or repair breaks in underground piping.</t>
+  </si>
+  <si>
+    <t>Break asphalt and other pavement so that pipes can be accessed, using airhammers, picks, and shovels. | Clean and disinfect domestic basements and other areas flooded by sewer stoppages. | Clean and repair septic tanks, sewer lines, or related structures such as manholes, culverts, and catch basins. | Communicate with supervisors and other workers, using equipment such as wireless phones, pagers, or radio telephones. | Cover repaired pipes with dirt, and pack backfilled excavations, using air and gasoline tampers. | Cut damaged sections of pipe with cutters, remove broken sections from ditches, and replace pipe sections, using pipe sleeves. | Dig out sewer lines manually, using shovels. | Drive trucks to transport crews, materials, and equipment. | Ensure that repaired sewer line joints are tightly sealed before backfilling begins. | Inspect manholes to locate sewer line stoppages. | Install rotary knives on flexible cables mounted on machine reels, according to the diameters of pipes to be cleaned. | Locate problems, using specially designed equipment, and mark where digging must occur to reach damaged tanks or pipes. | Measure excavation sites, using plumbers' snakes, tapelines, or lengths of cutting heads within sewers, and mark areas for digging. | Operate sewer cleaning equipment, including power rodders, high-velocity water jets, sewer flushers, bucket machines, wayne balls, and vac-alls. | Prepare and keep records of actions taken, including maintenance and repair work. | Requisition or order tools and equipment. | Rotate cleaning rods manually, using turning pins. | Service, adjust, and make minor repairs to equipment, machines, and attachments. | Start machines to feed revolving cables or rods into openings, stopping machines and changing knives to conform to pipe sizes. | Tap mainline sewers to install sewer saddles. | Update sewer maps and manhole charts. | Withdraw cables from pipes and examine them for evidence of mud, roots, grease, and other deposits indicating broken or clogged sewer lines.</t>
+  </si>
+  <si>
+    <t>47-4091.00</t>
+  </si>
+  <si>
+    <t>Segmental Pavers</t>
+  </si>
+  <si>
+    <t>Cutter | Paver | Paver Installer | Paver Layer | Paving Stone Installer | Segmental Wall Installer</t>
+  </si>
+  <si>
+    <t>Database software | Decorative Software Online Visualizers | Depiction Software Deco-Con | Depiction Software Deco-Con Estimator | Depiction Software Hardscape Imaging | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | UNI-GROUP Lockpave Pro | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Oral Comprehension | Oral Expression | Control Precision | Near Vision | Manual Dexterity | Arm-Hand Steadiness | Problem Sensitivity | Speech Recognition | Speech Clarity | Information Ordering | Static Strength | Finger Dexterity | Inductive Reasoning | Deductive Reasoning | Depth Perception | Trunk Strength | Reaction Time | Visualization | Category Flexibility | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Deal With External Customers or the Public in General | Contact With Others | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Time Pressure | Work Outcomes and Results of Other Workers | Frequency of Decision Making | Conflict Situations | Written Letters and Memos | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Impact of Decisions on Co-workers or Company Results | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Carpenters | Carpet Installers | Cement Masons and Concrete Finishers | Construction Laborers | Drywall and Ceiling Tile Installers | Floor Layers, Except Carpet, Wood, and Hard Tiles | Floor Sanders and Finishers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Roofers | Insulation Workers, Floor, Ceiling, and Wall | Paving, Surfacing, and Tamping Equipment Operators | Plasterers and Stucco Masons | Rail-Track Laying and Maintenance Equipment Operators | Rock Splitters, Quarry | Roofers | Stone Cutters and Carvers, Manufacturing | Stonemasons | Terrazzo Workers and Finishers | Tile and Stone Setters</t>
+  </si>
+  <si>
+    <t>Lay out, cut, and place segmental paving units. Includes installers of bedding and restraining materials for the paving units.</t>
+  </si>
+  <si>
+    <t>Cement the edges of the paved area. | Compact bedding sand and pavers to finish the paved area, using a plate compactor. | Cut paving stones to size and for edges, using a splitter and a masonry saw. | Design paver installation layout pattern and create markings for directional references of joints and stringlines. | Discuss the design with the client. | Prepare base for installation by removing unstable or unsuitable materials, compacting and grading the soil, draining or stabilizing weak or saturated soils and taking measures to prevent water penetration and migration of bedding sand. | Resurface an outside area with cobblestones, terracotta tiles, concrete or other materials. | Screed sand level to an even thickness, and recheck sand exposed to elements, raking and rescreeding if necessary. | Set pavers, aligning and spacing them correctly. | Supply and place base materials, edge restraints, bedding sand and jointing sand. | Sweep sand from the surface prior to opening to traffic. | Sweep sand into the joints and compact pavement until the joints are full.</t>
+  </si>
+  <si>
+    <t>47-4099.00</t>
+  </si>
+  <si>
+    <t>Construction and Related Workers, All Other</t>
+  </si>
+  <si>
+    <t>Concrete Cutter | Construction Worker | Demolition Worker | Foundation Repair Technician | Scaffold Erector | Shoring Worker | Waterproofing Technician | Construction Specialist | Curb Setter | Building Restoration Worker</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Building and Construction | Mechanical | English Language | Public Safety and Security | Mathematics | Design | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Carpenters | Cement Masons and Concrete Finishers | Brickmasons and Blockmasons | Stonemasons | Segmental Pavers | Fence Erectors | Hazardous Materials Removal Workers | Highway Maintenance Workers | Septic Tank Servicers and Sewer Pipe Cleaners | Construction and Building Inspectors | Weatherization Installers and Technicians | Insulation Workers, Floor, Ceiling, and Wall | Operating Engineers and Other Construction Equipment Operators | Structural Iron and Steel Workers | Roofers | Glaziers | Manufactured Building and Mobile Home Installers | First-Line Supervisors of Construction Trades and Extraction Workers | Helpers, Construction Trades, All Other</t>
+  </si>
+  <si>
+    <t>All construction and related workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform construction and related work in specialties not classified separately. | Read blueprints, sketches, and specifications to determine work requirements. | Measure, mark, and lay out work areas and material placement. | Cut, drill, saw, and shape construction materials using hand and power tools. | Install, assemble, and fasten structural and finish components. | Erect and dismantle forms, shoring, scaffolding, and temporary structures. | Apply coatings, sealants, and waterproofing materials to surfaces. | Demolish and remove existing structures, fixtures, and materials. | Operate small construction equipment and powered tools safely. | Inspect completed work for conformance to plans and quality standards. | Follow site safety plans, fall protection, and hazard communication rules. | Maintain and clean tools, equipment, and work areas. | Coordinate work with other trades and site supervisors. | Estimate material quantities and request supplies as needed.</t>
+  </si>
+  <si>
+    <t>47-4099.03</t>
+  </si>
+  <si>
+    <t>Weatherization Installers and Technicians</t>
+  </si>
+  <si>
+    <t>Energy Administrator | Field Technician | Weatherization Installer | Weatherization Technician | Weatherization Worker | Weatherization and Housing Inspector</t>
+  </si>
+  <si>
+    <t>Database software | Energy auditing software | Energy use ratings databases | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | SAP software | Salesforce.com Salesforce CRM | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Building and Construction | Customer and Personal Service | Mechanical | Administration and Management | Education and Training | Mathematics | English Language | Public Safety and Security | Administrative | Computers and Electronics | Economics and Accounting | Production and Processing | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Manual Dexterity | Oral Comprehension | Oral Expression | Information Ordering | Arm-Hand Steadiness | Multilimb Coordination | Visualization | Flexibility of Closure | Depth Perception | Far Vision | Extent Flexibility | Trunk Strength | Speech Clarity | Speech Recognition | Visual Color Discrimination | Reaction Time | Control Precision | Finger Dexterity | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Telephone Conversations | Work With or Contribute to a Work Group or Team | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Cramped Work Space, Awkward Positions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Hazardous Equipment | Time Pressure | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Deal With External Customers or the Public in General | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | E-Mail | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Indoors, Not Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Boilermakers | Construction Managers | Construction and Building Inspectors | Energy Auditors | Energy Engineers, Except Wind and Solar | Geothermal Technicians | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Maintenance and Repair Workers, General | Plumbers, Pipefitters, and Steamfitters | Roofers | Sheet Metal Workers | Solar Energy Installation Managers | Solar Photovoltaic Installers | Solar Thermal Installers and Technicians | Stationary Engineers and Boiler Operators | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Perform a variety of activities to weatherize homes and make them more energy efficient. Duties include repairing windows, insulating ducts, and performing heating, ventilating, and air-conditioning (HVAC) work. May perform energy audits and advise clients on energy conservation measures.</t>
+  </si>
+  <si>
+    <t>Apply insulation materials, such as loose, blanket, board, and foam insulation to attics, crawl spaces, basements, or walls. | Apply spackling, compounding, or other materials to repair holes in walls. | Clean and maintain tools and equipment. | Contact residents or building owners to schedule appointments. | Determine amount of air leakage in buildings, using a blower door machine. | Explain energy conservation measures, such as the use of low flow showerheads and energy-efficient lighting. | Explain recommendations, policies, procedures, requirements, or other related information to residents or building owners. | Inspect buildings to identify required weatherization measures, including repair work, modification, or replacement. | Install and seal air ducts, combustion air openings, or ventilation openings to improve heating and cooling efficiency. | Install storm windows or storm doors and verify proper fit. | Maintain activity logs, financial transaction logs, or other records of weatherization work performed. | Make minor repairs using basic hand or power tools and materials, such as glass, lumber, and drywall. | Prepare and apply weather-stripping, glazing, caulking, or door sweeps to reduce energy losses. | Prepare cost estimates or specifications for rehabilitation or weatherization services. | Prepare or assist in the preparation of bids, contracts, or written reports related to weatherization work. | Recommend weatherization techniques to clients in accordance with needs and applicable energy regulations, codes, policies, or statutes. | Test and diagnose air flow systems, using furnace efficiency analysis equipment. | Test combustible appliances, such as gas appliances. | Wrap air ducts and water lines with insulating materials, such as duct wrap and pipe insulation. | Wrap water heaters with water heater blankets.</t>
+  </si>
+  <si>
+    <t>47-5011.00</t>
+  </si>
+  <si>
+    <t>Derrick Operators, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Derrick Hand | Derrick Man | Derrick Operator | Derrick Worker | Floor Hand</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | English Language | Education and Training</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Control Precision | Arm-Hand Steadiness | Manual Dexterity | Reaction Time | Problem Sensitivity | Static Strength | Extent Flexibility | Auditory Attention | Hearing Sensitivity | Depth Perception | Stamina | Trunk Strength | Deductive Reasoning | Oral Expression | Flexibility of Closure | Selective Attention | Far Vision | Gross Body Equilibrium | Speech Clarity | Speech Recognition | Gross Body Coordination | Near Vision | Finger Dexterity | Response Orientation | Oral Comprehension | Inductive Reasoning | Perceptual Speed | Visualization | Information Ordering | Speed of Limb Movement | Rate Control | Visual Color Discrimination | Speed of Closure | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Conditions | Exposed to High Places | Contact With Others | Work With or Contribute to a Work Group or Team | Spend Time Standing | Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Exposed to Extremely Bright or Inadequate Lighting Conditions | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Frequency of Decision Making | Freedom to Make Decisions | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Exposed to Cramped Work Space, Awkward Positions | Exposed to Whole Body Vibration | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Continuous Mining Machine Operators | Crane and Tower Operators | Dredge Operators | Earth Drillers, Except Oil and Gas | Electrical Power-Line Installers and Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Explosives Workers, Ordnance Handling Experts, and Blasters | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Riggers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Rig derrick equipment and operate pumps to circulate mud or fluid through drill hole.</t>
+  </si>
+  <si>
+    <t>Clamp holding fixtures on ends of hoisting cables. | Control the viscosity and weight of the drilling fluid. | Guide lengths of pipe into and out of elevators. | Inspect derricks for flaws, and clean and oil derricks to maintain proper working conditions. | Inspect derricks, or order their inspection, prior to being raised or lowered. | Listen to mud pumps and check regularly for vibration and other problems to ensure that rig pumps and drilling mud systems are working properly. | Position and align derrick elements, using harnesses and platform climbing devices. | Prepare mud reports, and instruct crews about the handling of any chemical additives. | Repair pumps, mud tanks, and related equipment. | Set and bolt crown blocks to posts at tops of derricks. | Start pumps that circulate mud through drill pipes and boreholes to cool drill bits and flush out drill cuttings. | Steady pipes during connection to or disconnection from drill or casing strings. | String cables through pulleys and blocks. | Supervise crew members, and provide assistance in training them. | Weigh clay, and mix with water and chemicals to make drilling mud, using portable mixers.</t>
+  </si>
+  <si>
+    <t>47-5012.00</t>
+  </si>
+  <si>
+    <t>Rotary Drill Operators, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Daylight Driller | Drill Operator | Driller | Drilling Rig Operator | Motor Man | Oil Rig Driller | Oil Well Driller | Relief Driller | Tool Pusher</t>
+  </si>
+  <si>
+    <t>CAPSHER Technology SureTec | Drillingsoftware DrillPro | Drillingsoftware Tubular Database | Microsoft Excel | Microsoft Office software | Microsoft Word | Pason WellView Field Solution | Python | SAP software | Salesforce software | Schlumberger Petrel E&amp;P | Structure query language SQL</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking | Reading Comprehension | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Administration and Management | Education and Training | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Control Precision | Problem Sensitivity | Near Vision | Arm-Hand Steadiness | Manual Dexterity | Multilimb Coordination | Oral Expression | Information Ordering | Oral Comprehension | Finger Dexterity | Inductive Reasoning | Deductive Reasoning | Rate Control | Selective Attention | Written Expression | Perceptual Speed | Category Flexibility | Written Comprehension | Speech Clarity | Speech Recognition | Auditory Attention | Reaction Time | Visualization | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Consequence of Error | Exposed to Very Hot or Cold Temperatures | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment | Level of Competition | Spend Time Standing | Contact With Others | Freedom to Make Decisions | Exposed to Hazardous Conditions | Physical Proximity | Time Pressure | Determine Tasks, Priorities and Goals | Exposed to Whole Body Vibration | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to High Places | Pace Determined by Speed of Equipment | In an Open Vehicle or Operating Equipment | Spend Time Making Repetitive Motions | Outdoors, Under Cover | Exposed to Minor Burns, Cuts, Bites, or Stings | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Continuous Mining Machine Operators | Derrick Operators, Oil and Gas | Dredge Operators | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Explosives Workers, Ordnance Handling Experts, and Blasters | Helpers--Extraction Workers | Hoist and Winch Operators | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Operating Engineers and Other Construction Equipment Operators | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Plumbers, Pipefitters, and Steamfitters | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Tool Grinders, Filers, and Sharpeners | Wellhead Pumpers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up or operate a variety of drills to remove underground oil and gas, or remove core samples for testing during oil and gas exploration.</t>
+  </si>
+  <si>
+    <t>Bolt together pump and engine parts, and connect tanks and flow lines. | Cap wells with packers, or turn valves, to regulate outflow of oil from wells. | Clean and oil pulleys, blocks, and cables. | Connect sections of drill pipe, using hand tools and powered wrenches and tongs. | Count sections of drill rod to determine depths of boreholes. | Direct rig crews in drilling and other activities, such as setting up rigs and completing or servicing wells. | Line drilled holes with pipes, and install all necessary hardware, to prepare new wells. | Locate and recover lost or broken bits, casings, and drill pipes from wells, using special tools. | Maintain and adjust machinery to ensure proper performance. | Maintain records of footage drilled, location and nature of strata penetrated, materials and tools used, services rendered, and time required. | Monitor progress of drilling operations, and select and change drill bits according to the nature of strata, using hand tools. | Observe pressure gauge and move throttles and levers to control the speed of rotary tables, and to regulate pressure of tools at bottoms of boreholes. | Plug observation wells, and restore sites. | Position and prepare truck-mounted derricks at drilling areas specified on field maps. | Push levers and brake pedals to control gasoline, diesel, electric, or steam draw works that lower and raise drill pipes and casings in and out of wells. | Remove core samples during drilling to determine the nature of the strata being drilled. | Repair or replace defective parts of machinery, such as rotary drill rigs, water trucks, air compressors, and pumps, using hand tools. | Start and examine operation of slush pumps to ensure circulation and consistency of drilling fluid or mud in well. | Train crews, and introduce procedures to make drill work more safe and effective. | Weigh clay, and mix with water and chemicals to make drilling mud.</t>
+  </si>
+  <si>
+    <t>47-5013.00</t>
+  </si>
+  <si>
+    <t>Service Unit Operators, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Pulling Unit Operator | Reverse Unit Operator | Rig Operator | Service Operator | Service Rig Operator | Tool Pusher | Well Servicing Rig Operator | Wireline Operator</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | Data logger software | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | SAP software | Supervisory control and data acquisition SCADA software | Time and attendance software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Active Learning | Speaking | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Customer and Personal Service | Engineering and Technology | Public Safety and Security | Education and Training | English Language | Sales and Marketing | Chemistry | Administration and Management | Transportation | Production and Processing</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Arm-Hand Steadiness | Control Precision | Multilimb Coordination | Near Vision | Hearing Sensitivity | Reaction Time | Manual Dexterity | Selective Attention | Perceptual Speed | Oral Comprehension | Far Vision | Auditory Attention | Speech Recognition | Speech Clarity | Oral Expression | Inductive Reasoning | Flexibility of Closure | Deductive Reasoning | Static Strength | Visualization | Depth Perception | Visual Color Discrimination | Gross Body Equilibrium | Extent Flexibility | Trunk Strength | Rate Control | Finger Dexterity | Time Sharing | Written Comprehension | Category Flexibility | Information Ordering | Written Expression</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Contact With Others | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Conditions | Importance of Being Exact or Accurate | Time Pressure | Spend Time Standing | In an Enclosed Vehicle or Operate Enclosed Equipment | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Freedom to Make Decisions | Physical Proximity | Work Outcomes and Results of Other Workers | Exposed to Cramped Work Space, Awkward Positions | Importance of Repeating Same Tasks | Exposed to Minor Burns, Cuts, Bites, or Stings | Pace Determined by Speed of Equipment | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Exposed to High Places | Spend Time Making Repetitive Motions | Spend Time Bending or Twisting Your Body | In an Open Vehicle or Operating Equipment | Level of Competition | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Chemical Plant and System Operators | Continuous Mining Machine Operators | Earth Drillers, Except Oil and Gas | Engine and Other Machine Assemblers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Petroleum Pump System Operators, Refinery Operators, and Gaugers | Plumbers, Pipefitters, and Steamfitters | Power Plant Operators | Pump Operators, Except Wellhead Pumpers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Septic Tank Servicers and Sewer Pipe Cleaners | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Operate equipment to increase oil flow from producing wells or to remove stuck pipe, casing, tools, or other obstructions from drilling wells. Includes fishing-tool technicians.</t>
+  </si>
+  <si>
+    <t>Apply green technologies or techniques, such as the use of coiled tubing, slim-hole drilling, horizontal drilling, hydraulic fracturing, or gas lift systems. | Close and seal wells no longer in use. | Confer with others to gather information regarding pipe or tool sizes or borehole conditions in wells. | Direct drilling crews performing activities such as assembling and connecting pipe, applying weights to drill pipes, or drilling around lodged obstacles. | Drive truck-mounted units to well sites. | Examine unserviceable wells to determine actions to be taken to improve well conditions. | Insert detection instruments into wells with obstructions. | Install pressure-control devices onto wellheads. | Interpret instrument readings to ascertain the depth of obstruction. | Listen to engines, rotary chains, or other equipment to detect faulty operations or unusual well conditions. | Maintain and perform safety inspections on equipment and tools. | Monitor sound wave-generating or detecting mechanisms to determine well fluid levels. | Operate controls that raise derricks or level rigs. | Operate pumps that circulate water, oil, or other fluids through wells to remove sand or other materials obstructing the free flow of oil. | Operate specialized equipment to remove obstructions by backing off or severing pipes by chemical or explosive action. | Perforate well casings or sidewalls of boreholes with explosive charges. | Prepare reports of services rendered, tools used, or time required, for billing purposes. | Select fishing methods or tools for removing obstacles such as liners, broken casing, screens, or drill pipe. | Thread cables through derrick pulleys, using hand tools.</t>
+  </si>
+  <si>
+    <t>47-5022.00</t>
+  </si>
+  <si>
+    <t>Excavating and Loading Machine and Dragline Operators, Surface Mining</t>
+  </si>
+  <si>
+    <t>Backhoe Operator | Dragline Oiler | Dragline Operator | Equipment Operator | Excavator Operator | Heavy Equipment Operator | Loader Operator | Pit Operator | Track Hoe Operator</t>
+  </si>
+  <si>
+    <t>Email software | Google Gmail | Machine control systems | Machine monitoring software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Learning | Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Depth Perception | Reaction Time | Manual Dexterity | Arm-Hand Steadiness | Response Orientation | Rate Control | Far Vision | Spatial Orientation | Near Vision | Auditory Attention | Finger Dexterity | Peripheral Vision | Hearing Sensitivity | Oral Comprehension | Problem Sensitivity | Oral Expression | Speech Recognition | Speech Clarity | Visual Color Discrimination | Static Strength | Speed of Limb Movement | Time Sharing | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Whole Body Vibration | Exposed to Contaminants | Frequency of Decision Making | Spend Time Making Repetitive Motions | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Sitting | Health and Safety of Other Workers | Pace Determined by Speed of Equipment | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Consequence of Error | Exposed to Very Hot or Cold Temperatures | In an Open Vehicle or Operating Equipment | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Construction Laborers | Continuous Mining Machine Operators | Crane and Tower Operators | Dredge Operators | Earth Drillers, Except Oil and Gas | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Rail-Track Laying and Maintenance Equipment Operators | Riggers | Rotary Drill Operators, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Operate or tend machinery at surface mining site, equipped with scoops, shovels, or buckets to excavate and load loose materials.</t>
+  </si>
+  <si>
+    <t>Adjust dig face angles for varying overburden depths and set lengths. | Become familiar with digging plans, machine capabilities and limitations, and efficient and safe digging procedures in a given application. | Create or maintain inclines or ramps. | Direct ground workers engaged in activities such as moving stakes or markers, or changing positions of towers. | Direct workers engaged in placing blocks or outriggers to prevent capsizing of machines when lifting heavy loads. | Drive machines to work sites. | Handle slides, mud, or pit cleanings or maintenance. | Lubricate, adjust, or repair machinery and replace parts, such as gears, bearings, or bucket teeth. | Measure and verify levels of rock or gravel, bases, or other excavated material. | Move levers, depress foot pedals, and turn dials to operate power machinery, such as power shovels, stripping shovels, scraper loaders, or backhoes. | Move materials over short distances, such as around a construction site, factory, or warehouse. | Observe hand signals, grade stakes, or other markings when operating machines so that work can be performed to specifications. | Operate machinery to perform activities such as backfilling excavations, vibrating or breaking rock or concrete, or making winter roads. | Perform manual labor to prepare or finish sites, such as shoveling materials by hand. | Receive written or oral instructions regarding material movement or excavation. | Set up or inspect equipment prior to operation.</t>
+  </si>
+  <si>
+    <t>47-5023.00</t>
+  </si>
+  <si>
+    <t>Earth Drillers, Except Oil and Gas</t>
+  </si>
+  <si>
+    <t>Blast Hole Driller | Diamond Driller | Drill Operator | Driller | Hard Rock Drill Operator | Highwall Drill Operator | Rock Drill Operator | Underground Drill Operator | Water Well Driller | Well Driller</t>
+  </si>
+  <si>
+    <t>Global positioning system GPS software | Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Administration and Management | Transportation | Public Safety and Security | Design</t>
+  </si>
+  <si>
+    <t>Control Precision | Arm-Hand Steadiness | Multilimb Coordination | Reaction Time | Manual Dexterity | Depth Perception | Near Vision | Rate Control | Perceptual Speed | Hearing Sensitivity | Oral Comprehension | Problem Sensitivity | Deductive Reasoning | Information Ordering | Visualization | Far Vision | Finger Dexterity | Inductive Reasoning | Visual Color Discrimination | Speech Clarity | Auditory Attention | Selective Attention | Flexibility of Closure | Written Expression | Oral Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Spend Time Making Repetitive Motions | Spend Time Standing | Determine Tasks, Priorities and Goals | Exposed to Whole Body Vibration | Contact With Others | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | In an Open Vehicle or Operating Equipment | Health and Safety of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Telephone Conversations | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Continuous Mining Machine Operators | Derrick Operators, Oil and Gas | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Excavating and Loading Machine and Dragline Operators, Surface Mining | Explosives Workers, Ordnance Handling Experts, and Blasters | Helpers--Extraction Workers | Hoist and Winch Operators | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Rail-Track Laying and Maintenance Equipment Operators | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Tool Grinders, Filers, and Sharpeners | Wellhead Pumpers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate a variety of drills such as rotary, churn, and pneumatic to tap subsurface water and salt deposits, to remove core samples during mineral exploration or soil testing, and to facilitate the use of explosives in mining or construction. Includes horizontal and earth boring machine operators.</t>
+  </si>
+  <si>
+    <t>Assemble and position machines, augers, casing pipes, and other equipment, using hand and power tools. | Create and lay out designs for drill and blast patterns. | Design well pumping systems. | Disinfect, reconstruct, and redevelop contaminated wells and water pumping systems, and clean and disinfect new wells in preparation for use. | Document geological formations encountered during work. | Drill or bore holes in rock for blasting, grouting, anchoring, or building foundations. | Drive or guide truck-mounted equipment into position, level and stabilize rigs, and extend telescoping derricks. | Drive trucks, tractors, or truck-mounted drills to and from work sites. | Fabricate well casings. | Inspect core samples to determine nature of strata, or take samples to laboratories for analysis. | Monitor drilling operations, by checking gauges and listening to equipment to assess drilling conditions and to determine the need to adjust drilling or alter equipment. | Operate controls to stabilize machines and to position and align drills. | Operate machines to flush earth cuttings or to blow dust from holes. | Operate water-well drilling rigs and other equipment to drill, bore, and dig for water wells or for environmental assessment purposes. | Perform pumping tests to assess well performance. | Perform routine maintenance and upgrade work on machines and equipment, such as replacing parts, building up drill bits, and lubricating machinery. | Place and install screens, casings, pumps, and other well fixtures to develop wells. | Pour water into wells, or pump water or slush into wells to cool drill bits and to remove drillings. | Record drilling progress and geological data. | Regulate air pressure, rotary speed, and downward pressure, according to the type of rock or concrete being drilled. | Retract augers to force discharge dirt from holes. | Retrieve lost equipment from bore holes, using retrieval tools and equipment. | Review client requirements and proposed locations for drilling operations to determine feasibility, and to determine cost estimates. | Select and attach drill bits and drill rods, adding more rods as hole depths increase, and changing drill bits as needed. | Select the appropriate drill for the job, using knowledge of rock or soil conditions. | Signal crane operators to move equipment. | Start, stop, and control drilling speed of machines and insertion of casings into holes. | Verify depths and alignments of boring positions. | Withdraw drill rods from holes, and extract core samples.</t>
+  </si>
+  <si>
+    <t>47-5032.00</t>
+  </si>
+  <si>
+    <t>Explosives Workers, Ordnance Handling Experts, and Blasters</t>
+  </si>
+  <si>
+    <t>Blast Hole Driller | Blaster | Explosive Technician | Powderman | Unexploded Ordnance Quality Control Officer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Blaster's Tool and Supply Company Blaster's Calculator | Datavis DBS Designer | DetNet ViewShot | ESRI ArcGIS software | Global positioning system GPS software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking | Reading Comprehension | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Law and Government | Mathematics | Engineering and Technology | Transportation | Customer and Personal Service | Administration and Management | English Language | Production and Processing | Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Manual Dexterity | Oral Comprehension | Deductive Reasoning | Inductive Reasoning | Information Ordering | Arm-Hand Steadiness | Oral Expression | Finger Dexterity | Multilimb Coordination | Reaction Time | Visual Color Discrimination | Control Precision | Selective Attention | Depth Perception | Speech Clarity | Category Flexibility | Flexibility of Closure | Perceptual Speed | Visualization | Speech Recognition | Far Vision | Hearing Sensitivity | Extent Flexibility | Trunk Strength | Static Strength | Time Sharing | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Conditions | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Importance of Being Exact or Accurate | Exposed to Contaminants | Contact With Others | Time Pressure | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Exposed to Hazardous Equipment | In an Enclosed Vehicle or Operate Enclosed Equipment | In an Open Vehicle or Operating Equipment | Freedom to Make Decisions | Physical Proximity | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Construction Laborers | Continuous Mining Machine Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Hazardous Materials Removal Workers | Helpers--Extraction Workers | Hoist and Winch Operators | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Pump Operators, Except Wellhead Pumpers | Riggers | Roof Bolters, Mining | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Place and detonate explosives to demolish structures or to loosen, remove, or displace earth, rock, or other materials. May perform specialized handling, storage, and accounting procedures.</t>
+  </si>
+  <si>
+    <t>Assemble and position equipment, explosives, and blasting caps in holes at specified depths, or load perforating guns or torpedoes with explosives. | Clean, gauge, and lubricate gun ports. | Compile and keep gun and explosives records in compliance with local and federal laws. | Connect electrical wire to primers, and cover charges or fill blast holes with clay, drill chips, sand, or other material. | Create and lay out designs for drill and blast patterns. | Cut specified lengths of primacord and attach primers to cord ends. | Document geological formations encountered during work. | Drive trucks to transport explosives and blasting equipment to blasting sites. | Examine blast areas to determine amounts and kinds of explosive charges needed and to ensure that safety laws are observed. | Insert waterproof sealers, bullets, and/or powder charges into guns, and screw gun ports back into place. | Insert, pack, and pour explosives, such as dynamite, ammonium nitrate, black powder, or slurries into blast holes; then shovel drill cuttings, admit water into boreholes, and tamp material to compact charges. | Lay primacord between rows of charged blast holes, and tie cord into main lines to form blast patterns. | Light fuses, drop detonating devices into wells or boreholes, or activate firing devices with plungers, dials, or buttons, in order to set off single or multiple blasts. | Lower perforating guns into wells, using hoists; then use measuring devices and instrument panels to position guns in correct positions for taking samples. | Maintain inventory levels, ordering new supplies as necessary. | Mark patterns, locations, and depths of charge holes for drilling, and issue drilling instructions. | Measure depths of drilled blast holes, using weighted tape measures. | Move and store inventories of explosives, loaded perforating guns, and other materials, according to established safety procedures. | Operate machines to flush earth cuttings or to blow dust from holes. | Place explosive charges in holes or other spots; then detonate explosives to demolish structures or to loosen, remove, or displace earth, rock, or other materials. | Place safety cones around blast areas to alert other workers of danger zones, and signal workers as necessary to ensure that they clear blast sites prior to explosions. | Repair and service blasting, shooting, and automotive equipment, and electrical wiring and instruments, using hand tools. | Set up and operate equipment such as hoists, jackhammers, and drills, in order to bore charge holes. | Set up and operate short-wave radio or field telephone equipment to transmit and receive blast information. | Signal crane operators to move equipment. | Tie specified lengths of delaying fuses into patterns in order to time sequences of explosions. | Verify detonation of charges by observing control panels, or by listening for the sounds of blasts.</t>
+  </si>
+  <si>
+    <t>47-5041.00</t>
+  </si>
+  <si>
+    <t>Continuous Mining Machine Operators</t>
+  </si>
+  <si>
+    <t>Bore Miner Operator | Continuous Miner | Continuous Miner Operator (CMO) | Continuous Mining Machine Operator | Continuous Mining Operator (CMO) | Heavy Equipment Operator | Loader Operator | Mine Technician | Mine Utility Operator | Miner Operator</t>
+  </si>
+  <si>
+    <t>Fleet monitoring system software | Hitachi ZXLink | Leica Geosystems FMS | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Minitab</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Law and Government | Education and Training</t>
+  </si>
+  <si>
+    <t>Control Precision | Arm-Hand Steadiness | Problem Sensitivity | Multilimb Coordination | Reaction Time | Near Vision | Rate Control | Hearing Sensitivity | Depth Perception | Selective Attention | Far Vision | Manual Dexterity | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Oral Expression | Extent Flexibility | Trunk Strength | Response Orientation | Auditory Attention | Visual Color Discrimination | Static Strength | Finger Dexterity | Time Sharing | Visualization | Category Flexibility | Information Ordering</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Frequency of Decision Making | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Contact With Others | Consequence of Error | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Freedom to Make Decisions | Exposed to Extremely Bright or Inadequate Lighting Conditions | Exposed to Cramped Work Space, Awkward Positions | Spend Time Standing | Pace Determined by Speed of Equipment | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | Exposed to Whole Body Vibration | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Crane and Tower Operators | Dredge Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Loading and Moving Machine Operators, Underground Mining | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pile Driver Operators | Rail-Track Laying and Maintenance Equipment Operators | Roof Bolters, Mining | Rotary Drill Operators, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Operate self-propelled mining machines that rip coal, metal and nonmetal ores, rock, stone, or sand from the mine face and load it onto conveyors, shuttle cars, or trucks in a continuous operation.</t>
+  </si>
+  <si>
+    <t>Apply new technologies developed to minimize the environmental impact of coal mining. | Check the stability of roof and rib support systems before mining face areas. | Conduct methane gas checks to ensure breathing quality of air. | Determine locations, boundaries, and depths of holes or channels to be cut. | Drive machines into position at working faces. | Guide and assist crews laying track and resetting supports and blocking. | Hang ventilation tubing and ventilation curtains to ensure that the mining face area is kept properly ventilated. | Install casings to prevent cave-ins. | Move controls to start and regulate movement of conveyors and to start and position drill cutters or torches. | Move levers to raise and lower hydraulic safety bars supporting roofs above machines until other workers complete framing. | Observe and listen to equipment operation to detect binding or stoppage of tools or other equipment malfunctions. | Operate mining machines to gather coal and convey it to floors or shuttle cars. | Repair, oil, and adjust machines, and change cutting teeth, using wrenches. | Reposition machines to make additional holes or cuts. | Scrape or wash conveyors, using belt scrapers or belt washers, to minimize dust production.</t>
+  </si>
+  <si>
+    <t>47-5043.00</t>
+  </si>
+  <si>
+    <t>Roof Bolters, Mining</t>
+  </si>
+  <si>
+    <t>Bolt Machine Operator | Bolt Man | Bolter | Miner | Place Change Roof Bolter | Roof Bolter | Roof Bolter Operator | Underground Miner | Underground Roof Bolter</t>
+  </si>
+  <si>
+    <t>Caterpillar Cat MineStar System | Caterpillar Command</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Education and Training | Mechanical | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Control Precision | Arm-Hand Steadiness | Extent Flexibility | Manual Dexterity | Problem Sensitivity | Multilimb Coordination | Reaction Time | Near Vision | Depth Perception | Information Ordering | Static Strength | Selective Attention | Response Orientation | Rate Control | Trunk Strength | Far Vision | Gross Body Equilibrium | Stamina | Speech Recognition | Speech Clarity | Auditory Attention | Hearing Sensitivity | Finger Dexterity | Time Sharing | Visualization | Deductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Exposed to Contaminants | Spend Time Making Repetitive Motions | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Pace Determined by Speed of Equipment | Spend Time Bending or Twisting Your Body | Exposed to Cramped Work Space, Awkward Positions | Contact With Others | Indoors, Not Environmentally Controlled | Spend Time Walking or Running | Exposed to Whole Body Vibration | Physical Proximity | Importance of Being Exact or Accurate | Consequence of Error | Work Outcomes and Results of Other Workers | Importance of Repeating Same Tasks | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Carpenters | Continuous Mining Machine Operators | Crane and Tower Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Explosives Workers, Ordnance Handling Experts, and Blasters | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Helpers--Extraction Workers | Hoist and Winch Operators | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Rail-Track Laying and Maintenance Equipment Operators | Reinforcing Iron and Rebar Workers | Riggers | Rotary Drill Operators, Oil and Gas | Sheet Metal Workers | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Operate machinery to install roof support bolts in underground mine.</t>
+  </si>
+  <si>
+    <t>Drill bolt holes into roofs at specified distances from ribs or adjacent bolts. | Drill test holes and test bolts for specified tension, using torque wrenches. | Dust rocks after bolting. | Force bolts into holes, using hydraulic mechanisms of self-propelled bolting machines. | Install various types of bolts, including truss, glue, and resin bolts, traversing entire ceiling spans. | Perform safety checks on equipment before operating. | Perform tests to determine if methane gas is present. | Perform ventilation tasks, such as hanging ventilation curtains and tubes. | Position bolting machines, and insert drill bits into chucks. | Position safety jacks to support underground mine roofs until bolts can be installed. | Pull down loose rock that cannot be supported. | Remove drill bits from chucks after drilling holes, and insert bolts into chucks. | Rotate chucks to turn bolts and open expansion heads against rock formations. | Tighten ends of anchored truss bolts, using turnbuckles.</t>
+  </si>
+  <si>
+    <t>47-5044.00</t>
+  </si>
+  <si>
+    <t>Loading and Moving Machine Operators, Underground Mining</t>
+  </si>
+  <si>
+    <t>Coal Hauler Operator | Equipment Operator | Load Haul Dump Operator (LHD Operator) | Loader Operator | Loading Machine Operator | Miner Operator | Production Miner | Ram Car Operator | Shuttle Car Operator | Underground Miner</t>
+  </si>
+  <si>
+    <t>Automated systems software | Inventory management systems | Maintenance management software | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Mine maintenance software | Work time accounting software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Education and Training</t>
+  </si>
+  <si>
+    <t>Control Precision | Reaction Time | Multilimb Coordination | Problem Sensitivity | Arm-Hand Steadiness | Manual Dexterity | Rate Control | Near Vision | Selective Attention | Perceptual Speed | Depth Perception | Trunk Strength | Time Sharing | Speech Clarity | Speech Recognition | Auditory Attention | Far Vision | Extent Flexibility | Visualization | Category Flexibility | Information Ordering | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Hazardous Equipment | Exposed to Hazardous Conditions | Work With or Contribute to a Work Group or Team | Exposed to Whole Body Vibration | In an Open Vehicle or Operating Equipment | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Making Repetitive Motions | Exposed to Cramped Work Space, Awkward Positions | Spend Time Bending or Twisting Your Body | Pace Determined by Speed of Equipment | Time Pressure | Contact With Others | Determine Tasks, Priorities and Goals | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists | Continuous Mining Machine Operators | Conveyor Operators and Tenders | Crane and Tower Operators | Excavating and Loading Machine and Dragline Operators, Surface Mining | Heavy and Tractor-Trailer Truck Drivers | Helpers--Extraction Workers | Hoist and Winch Operators | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Logging Equipment Operators | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Rail Car Repairers | Rail-Track Laying and Maintenance Equipment Operators | Riggers | Tank Car, Truck, and Ship Loaders</t>
+  </si>
+  <si>
+    <t>Operate underground loading or moving machine to load or move coal, ore, or rock using shuttle or mine car or conveyors. Equipment may include power shovels, hoisting engines equipped with cable-drawn scraper or scoop, or machines equipped with gathering arms and conveyor.</t>
+  </si>
+  <si>
+    <t>Advance machines to gather material and convey it into cars. | Clean hoppers, and clean spillage from tracks, walks, driveways, and conveyor decking. | Clean, fuel, service, and perform safety checks on all equipment, and repair and replace parts as necessary. | Control conveyors that run the entire length of shuttle cars to distribute loads as loading progresses. | Direct other workers to move stakes, place blocks, position anchors or cables, or move materials. | Drive loaded shuttle cars to ramps and move controls to discharge loads into mine cars or onto conveyors. | Drive machines into piles of material blasted from working faces. | Examine roadway and clear obstructions from the path of travel. | Guide and stop cars by switching, applying brakes, or placing scotches, or wooden wedges, between wheels and rails. | Handle high voltage sources and hang electrical cables. | Maintain records of materials moved. | Measure, weigh, or verify levels of rock, gravel, or other excavated material to prevent equipment overloads. | Monitor loading processes to ensure that materials are loaded according to specifications. | Move mine cars into position for loading and unloading, using pinchbars inserted under car wheels to position cars under loading spouts. | Move trailing electrical cables clear of obstructions, using rubber safety gloves. | Observe and record car numbers, carriers, customers, tonnages, and grades and conditions of material. | Observe hand signals, grade stakes, or other markings when operating machines. | Oil, lubricate, and adjust conveyors, crushers, and other equipment, using hand tools and lubricating equipment. | Operate levers to move conveyor booms or shovels so that mine contents such as coal, rock, and ore can be placed into cars or onto conveyors. | Pry off loose material from roofs and move it into the paths of machines, using crowbars. | Push or ride cars down slopes, or hook cars to cables and control cable drum brakes, to ease cars down inclines. | Read written instructions or confer with supervisors about schedules and materials to be moved. | Replace hydraulic hoses, headlight bulbs, and gathering-arm teeth. | Signal workers to move loaded cars. | Stop gathering arms when cars are full.</t>
+  </si>
+  <si>
+    <t>47-5049.00</t>
+  </si>
+  <si>
+    <t>Underground Mining Machine Operators, All Other</t>
+  </si>
+  <si>
+    <t>Longwall Machine Operator | Mine Machine Operator | Mining Machine Operator | Shuttle Car Operator | Underground Equipment Operator | Underground Miner | Underground Mining Machine Operator | Cutting Machine Operator | Mine Shuttle Operator | Continuous Miner Helper</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS | Supervisory control and data acquisition SCADA software</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | English Language | Engineering and Technology | Mathematics | Production and Processing | Physics</t>
+  </si>
+  <si>
+    <t>Exposed to Cramped Work Space, Awkward Positions | Exposed to Hazardous Equipment | Exposed to Hazardous Conditions | Exposed to Contaminants | Exposed to Whole Body Vibration | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Indoors, Not Environmentally Controlled | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Health and Safety of Other Workers | Consequence of Error | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Kneeling, Crouching, Stooping, or Crawling | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures</t>
+  </si>
+  <si>
+    <t>Continuous Mining Machine Operators | Roof Bolters, Mining | Loading and Moving Machine Operators, Underground Mining | Excavating and Loading Machine and Dragline Operators, Surface Mining | Earth Drillers, Except Oil and Gas | Explosives Workers, Ordnance Handling Experts, and Blasters | Rock Splitters, Quarry | Helpers--Extraction Workers | Extraction Workers, All Other | Mining and Geological Engineers, Including Mining Safety Engineers | First-Line Supervisors of Construction Trades and Extraction Workers | Operating Engineers and Other Construction Equipment Operators | Mobile Heavy Equipment Mechanics, Except Engines | Industrial Machinery Mechanics | Conveyor Operators and Tenders | Hoist and Winch Operators | Occupational Health and Safety Technicians | Geological Technicians, Except Hydrologic Technicians | Construction Laborers | Heavy and Tractor-Trailer Truck Drivers</t>
+  </si>
+  <si>
+    <t>All underground mining machine operators not listed separately.</t>
+  </si>
+  <si>
+    <t>Operate underground mining machinery in roles not classified separately. | Position, operate, and move self-propelled mining machines along working faces. | Cut, load, and transport coal, ore, and rock from the working face. | Monitor machine gauges, controls, and cutting performance during operation. | Inspect equipment before and after shifts and report defects. | Perform routine lubrication, bit changes, and minor repairs on machinery. | Follow ventilation, roof control, and gas monitoring procedures. | Install and check temporary roof supports in work areas. | Communicate with crew members using signals, radios, and phones. | Comply with mine safety regulations and emergency evacuation procedures. | Record production quantities, machine hours, and downtime. | Clear spillage, debris, and obstructions from haulage routes. | Assist with the extension of conveyors, track, and power cables. | Wear and maintain self-rescue devices and protective equipment.</t>
+  </si>
+  <si>
+    <t>47-5051.00</t>
+  </si>
+  <si>
+    <t>Rock Splitters, Quarry</t>
+  </si>
+  <si>
+    <t>Driller | Quarry Worker | Rock Splitter | Splitter Operator | Stone Breaker | Stone Splitter</t>
+  </si>
+  <si>
+    <t>Apache HTTP Server | Autodesk AutoCAD | Facebook | Maintenance reporting software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | SAP software | Time reporting software</t>
+  </si>
+  <si>
+    <t>Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Mathematics | Production and Processing | English Language | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Multilimb Coordination | Static Strength | Control Precision | Trunk Strength | Manual Dexterity | Near Vision | Extent Flexibility | Stamina | Dynamic Strength | Finger Dexterity | Visualization | Problem Sensitivity | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Exposed to Contaminants | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | Importance of Being Exact or Accurate | Exposed to Whole Body Vibration | In an Open Vehicle or Operating Equipment | Spend Time Bending or Twisting Your Body | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Brickmasons and Blockmasons | Cement Masons and Concrete Finishers | Construction Laborers | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Earth Drillers, Except Oil and Gas | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Helpers--Extraction Workers | Molders, Shapers, and Casters, Except Metal and Plastic | Pipelayers | Rotary Drill Operators, Oil and Gas | Sawing Machine Setters, Operators, and Tenders, Wood | Segmental Pavers | Stone Cutters and Carvers, Manufacturing | Stonemasons | Terrazzo Workers and Finishers | Tile and Stone Setters | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Separate blocks of rough dimension stone from quarry mass using jackhammers, wedges, or chop saws.</t>
+  </si>
+  <si>
+    <t>Cut grooves along outlines, using chisels. | Cut slabs of stone into sheets that will be used for floors or counters. | Drill holes along outlines, using jackhammers. | Drill holes into sides of stones broken from masses, insert dogs or attach slings, and direct removal of stones. | Insert wedges and feathers into holes, and drive wedges with sledgehammers to split stone sections from masses. | Locate grain line patterns to determine how rocks will split when cut. | Mark dimensions or outlines on stone prior to cutting, using rules and chalk lines. | Remove pieces of stone from larger masses, using jackhammers, wedges, and other tools. | Set charges of explosives to split rock.</t>
+  </si>
+  <si>
+    <t>47-5071.00</t>
+  </si>
+  <si>
+    <t>Roustabouts, Oil and Gas</t>
+  </si>
+  <si>
+    <t>Field Service Roustabout | Floor Hand | Oil Field Roustabout | Oil and Gas Roustabout | Production Roustabout | Rig Hand | Roustabout | Roustabout Crew Pusher | Roustabout Hand | Roustabout Pusher</t>
+  </si>
+  <si>
+    <t>Database management systems | Enertia | Inventory management systems | Maintenance record software | Maintenance software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Windows XP | Microsoft Word | Purchasing software | SAP software | Telephony software | Token Ring</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Multilimb Coordination | Near Vision | Problem Sensitivity | Far Vision | Arm-Hand Steadiness | Control Precision | Static Strength | Trunk Strength | Extent Flexibility | Information Ordering | Oral Comprehension | Stamina | Speech Recognition | Auditory Attention | Hearing Sensitivity | Gross Body Equilibrium | Reaction Time | Rate Control | Finger Dexterity | Selective Attention | Depth Perception | Flexibility of Closure | Deductive Reasoning | Oral Expression | Visualization</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Contact With Others | Frequency of Decision Making | Telephone Conversations | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Time Pressure | Indoors, Not Environmentally Controlled | Spend Time Standing | Exposed to Contaminants | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Freedom to Make Decisions | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Derrick Operators, Oil and Gas | Earth Drillers, Except Oil and Gas | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Hoist and Winch Operators | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Plumbers, Pipefitters, and Steamfitters | Riggers | Rotary Drill Operators, Oil and Gas | Service Unit Operators, Oil and Gas | Wellhead Pumpers</t>
+  </si>
+  <si>
+    <t>Assemble or repair oil field equipment using hand and power tools. Perform other tasks as needed.</t>
+  </si>
+  <si>
+    <t>Bolt together pump and engine parts. | Clean trucks used in the fields. | Clean up spilled oil by bailing it into barrels. | Cut down and remove trees and brush to clear drill sites, to reduce fire hazards, and to make way for roads to sites. | Dig drainage ditches around wells and storage tanks. | Dig holes, set forms, and mix and pour concrete into forms to make foundations for wood or steel derricks. | Dismantle and repair oil field machinery, boilers, and steam engine parts, using hand tools and power tools. | Guide cranes to move loads about decks. | Lay gas and oil pipelines. | Move pipes to and from trucks, using truck winches and motorized lifts, or by hand. | Supply equipment to rig floors as requested and provide assistance to roughnecks. | Unscrew or tighten pipes, casing, tubing, and pump rods, using hand and power wrenches and tongs. | Walk flow lines to locate leaks, using electronic detectors and by making visual inspections, and repair the leaks.</t>
+  </si>
+  <si>
+    <t>47-5081.00</t>
+  </si>
+  <si>
+    <t>Helpers--Extraction Workers</t>
+  </si>
+  <si>
+    <t>Continuous Miner Operator Helper | Driller Helper | Driller's Assistant | Longwall Machine Operator Helper | Miner Helper | Powderman | Salt Miner</t>
+  </si>
+  <si>
+    <t>Google Docs | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Transportation | Mathematics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Reaction Time | Control Precision | Static Strength | Problem Sensitivity | Near Vision | Far Vision | Trunk Strength | Depth Perception | Rate Control | Finger Dexterity | Oral Comprehension | Information Ordering | Selective Attention | Extent Flexibility | Stamina | Response Orientation | Visualization | Perceptual Speed | Deductive Reasoning | Auditory Attention | Hearing Sensitivity | Speech Recognition | Gross Body Equilibrium | Gross Body Coordination | Dynamic Strength | Spatial Orientation | Flexibility of Closure | Inductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Outdoors, Exposed to All Weather Conditions | Indoors, Not Environmentally Controlled | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Contact With Others | Exposed to Hazardous Conditions | In an Open Vehicle or Operating Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Frequency of Decision Making | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | In an Enclosed Vehicle or Operate Enclosed Equipment | Importance of Being Exact or Accurate | Pace Determined by Speed of Equipment | Telephone Conversations | Consequence of Error | Work Outcomes and Results of Other Workers | Spend Time Bending or Twisting Your Body | Spend Time Standing | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Construction Laborers | Continuous Mining Machine Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Production Workers | Hoist and Winch Operators | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Operating Engineers and Other Construction Equipment Operators | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Service Unit Operators, Oil and Gas | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Help extraction craft workers, such as earth drillers, blasters and explosives workers, derrick operators, and mining machine operators, by performing duties requiring less skill. Duties include supplying equipment or cleaning work area.</t>
+  </si>
+  <si>
+    <t>Clean and prepare sites for excavation or boring. | Clean up work areas and remove debris after extraction activities are complete. | Collect and examine geological matter, using hand tools and testing devices. | Dig trenches. | Dismantle extracting and boring equipment used for excavation, using hand tools. | Drive moving equipment to transport materials and parts to excavation sites. | Load materials into well holes or into equipment, using hand tools. | Observe and monitor equipment operation during the extraction process to detect any problems. | Organize materials to prepare for use. | Provide assistance to extraction craft workers, such as earth drillers and derrick operators. | Repair and maintain automotive and drilling equipment, using hand tools. | Set up and adjust equipment used to excavate geological materials. | Signal workers to start geological material extraction or boring. | Unload materials, devices, and machine parts, using hand tools.</t>
+  </si>
+  <si>
+    <t>47-5099.00</t>
+  </si>
+  <si>
+    <t>Extraction Workers, All Other</t>
+  </si>
+  <si>
+    <t>Blaster Helper | Drilling Worker | Extraction Worker | Mine Worker | Oil Field Worker | Quarry Worker | Surface Miner | Well Service Worker | Mineral Extraction Worker | Drill Helper</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | English Language | Engineering and Technology | Mathematics | Production and Processing | Chemistry</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Whole Body Vibration | Exposed to Hazardous Conditions</t>
+  </si>
+  <si>
+    <t>Helpers--Extraction Workers | Roustabouts, Oil and Gas | Derrick Operators, Oil and Gas | Rotary Drill Operators, Oil and Gas | Service Unit Operators, Oil and Gas | Earth Drillers, Except Oil and Gas | Explosives Workers, Ordnance Handling Experts, and Blasters | Rock Splitters, Quarry | Excavating and Loading Machine and Dragline Operators, Surface Mining | Continuous Mining Machine Operators | Roof Bolters, Mining | Underground Mining Machine Operators, All Other | First-Line Supervisors of Construction Trades and Extraction Workers | Operating Engineers and Other Construction Equipment Operators | Construction Laborers | Wellhead Pumpers | Pump Operators, Except Wellhead Pumpers | Mining and Geological Engineers, Including Mining Safety Engineers | Petroleum Engineers | Geological Technicians, Except Hydrologic Technicians</t>
+  </si>
+  <si>
+    <t>All extraction workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform extraction work in roles not classified separately. | Set up, operate, and tend drilling, cutting, and extraction equipment. | Assemble and dismantle drilling rigs, pipe, and surface equipment. | Load, transport, and place explosives and blasting accessories as directed. | Monitor equipment performance and adjust controls to maintain production. | Inspect tools, cables, hoses, and machinery for wear and damage. | Perform routine maintenance, lubrication, and minor repairs on equipment. | Clear debris, spillage, and overburden from work areas. | Measure and record depths, volumes, production data, and material grades. | Follow safety regulations for confined spaces, gases, and heavy equipment. | Install and maintain ventilation, drainage, and support systems. | Communicate with crew and supervisors using radios and hand signals. | Assist with site preparation, reclamation, and environmental controls. | Handle and store hazardous materials according to regulations.</t>
+  </si>
+  <si>
+    <t>49-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Mechanics, Installers, and Repairers</t>
+  </si>
+  <si>
+    <t>Electrical and Instrumentation Supervisor (E and I Supervisor) | Facilities Maintenance Supervisor | Facility Maintenance Supervisor | Maintenance Coordinator | Maintenance Foreman | Maintenance Manager | Maintenance Planner | Maintenance Superintendent | Maintenance Supervisor | Service Manager</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Automated inventory software | ComputerEase construction accounting software | Computerized maintenance management system CMMS | Cost accounting software | Database software | Email software | HCSS HeavyBid | HCSS HeavyJob | IBM Domino | IBM Notes | Infor ERP SyteLine | Maintenance management software | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | Payroll software | Programmable logic controller PLC software | Recordkeeping software | SAP software | Scheduling software | Supervisory control and data acquisition SCADA software | Vehicle management software | WorkTech MAXIMO | Yardi software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking | Active Listening | Reading Comprehension | Active Learning | Learning Strategies | Writing</t>
+  </si>
+  <si>
+    <t>Administration and Management | Mechanical | Customer and Personal Service | Administrative | Personnel and Human Resources | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Speech Clarity | Problem Sensitivity | Information Ordering | Flexibility of Closure | Selective Attention | Far Vision | Category Flexibility | Written Expression | Visualization | Perceptual Speed | Auditory Attention | Hearing Sensitivity | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Number Facility | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | E-Mail | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Importance of Repeating Same Tasks | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Facilities Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Industrial Production Managers | Recycling Coordinators</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate the activities of mechanics, installers, and repairers. May also advise customers on recommended services. Excludes team or work leaders.</t>
+  </si>
+  <si>
+    <t>Compile operational or personnel records, such as time and production records, inventory data, repair or maintenance statistics, or test results. | Compute estimates and actual costs of factors such as materials, labor, or outside contractors. | Conduct or arrange for worker training in safety, repair, or maintenance techniques, operational procedures, or equipment use. | Confer with personnel, such as management, engineering, quality control, customer, or union workers' representatives, to coordinate work activities, resolve employee grievances, or identify and review resource needs. | Counsel employees about work-related issues and assist employees to correct job-skill deficiencies. | Design equipment configurations to meet personnel needs. | Determine schedules, sequences, and assignments for work activities, based on work priority, quantity of equipment, and skill of personnel. | Develop or implement electronic maintenance programs or computer information management systems. | Develop, implement, or evaluate maintenance policies and procedures. | Examine objects, systems, or facilities and analyze information to determine needed installations, services, or repairs. | Inspect and monitor work areas, examine tools and equipment, and provide employee safety training to prevent, detect, and correct unsafe conditions or violations of procedures and safety rules. | Inspect, test, and measure completed work, using devices such as hand tools or gauges to verify conformance to standards or repair requirements. | Interpret specifications, blueprints, or job orders to construct templates and lay out reference points for workers. | Investigate accidents or injuries and prepare reports of findings. | Meet with vendors or suppliers to discuss products used in repair work. | Monitor employees' work levels and review work performance. | Monitor tool and part inventories and the condition and maintenance of shops to ensure adequate working conditions. | Participate in budget preparation and administration, coordinating purchasing and documentation and monitoring departmental expenditures. | Perform skilled repair or maintenance operations, using equipment such as hand or power tools, hydraulic presses or shears, or welding equipment. | Recommend or initiate personnel actions, such as hires, promotions, transfers, discharges, or disciplinary measures. | Requisition materials and supplies, such as tools, equipment, or replacement parts. | Review, evaluate, accept, and coordinate completion of work bid from contractors.</t>
+  </si>
+  <si>
+    <t>49-2011.00</t>
+  </si>
+  <si>
+    <t>Computer, Automated Teller, and Office Machine Repairers</t>
+  </si>
+  <si>
+    <t>ATM Technician (Automated Teller Machine Technician) | Computer Repair Technician | Computer Technician | Copier Technician | Customer Service Engineer | Field Engineer | Field Service Engineer | Field Service Technician | Field Technician | Service Technician</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Call tracking software | Cisco Systems VPN Client | Database software | Debugging software | Email software | Extensible markup language XML | Extensible stylesheet language XSL | Hypertext markup language HTML | IBM Notes | IBM WebSphere | Inventory control system software | JavaScript | Linux | Macromedia Cold Fusion | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Exchange | Microsoft Hyperterminal | Microsoft Internet Explorer | Microsoft Office Live Meeting | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic.NET | Microsoft Windows | Microsoft Word | Norton AntiVirus | Personal computer diagnostic software | Scheduling software | ServiceNow | Structured query language SQL | Symantec Altiris Deployment Solution | Symantec Norton Utilities | Terminal emulation software | UNIX | Virus detection software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Customer and Personal Service | Mechanical | Engineering and Technology | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Oral Expression | Problem Sensitivity | Written Comprehension | Speech Clarity | Speech Recognition | Finger Dexterity | Visualization | Information Ordering | Inductive Reasoning | Deductive Reasoning | Control Precision | Manual Dexterity | Arm-Hand Steadiness | Visual Color Discrimination | Selective Attention | Category Flexibility | Written Expression</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Freedom to Make Decisions | E-Mail | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Deal With External Customers or the Public in General | Contact With Others | Frequency of Decision Making | Importance of Being Exact or Accurate | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Work With or Contribute to a Work Group or Team | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Audiovisual Equipment Installers and Repairers | Avionics Technicians | Calibration Technologists and Technicians | Camera and Photographic Equipment Repairers | Coin, Vending, and Amusement Machine Servicers and Repairers | Computer Numerically Controlled Tool Operators | Computer User Support Specialists | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Industrial Machinery Mechanics | Medical Equipment Repairers | Office Machine Operators, Except Computer | Robotics Technicians | Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Repair, maintain, or install computers, word processing systems, automated teller machines, and electronic office machines, such as duplicating and fax machines.</t>
+  </si>
+  <si>
+    <t>Advise customers concerning equipment operation, maintenance, or programming. | Align, adjust, or calibrate equipment according to specifications. | Analyze equipment performance records to assess equipment functioning. | Assemble machines according to specifications, using hand or power tools and measuring devices. | Calibrate testing instruments. | Clean, oil, or adjust mechanical parts to maintain machines' operating efficiency and to prevent breakdowns. | Complete repair bills, shop records, time cards, or expense reports. | Converse with customers to determine details of equipment problems. | Disassemble machines to examine parts, such as wires, gears, or bearings for wear or defects, using hand or power tools and measuring devices. | Enter information into computers to copy programs from one electronic component to another or to draw, modify, or store schematics. | Fill machines with toners, inks, or other duplicating fluids. | Install and configure new equipment, including operating software or peripheral equipment. | Lay cable and hook up electrical connections between machines, power sources, and phone lines. | Maintain parts inventories and order any additional parts needed for repairs. | Maintain records of equipment maintenance work or repairs. | Operate machines to test functioning of parts or mechanisms. | Read specifications, such as blueprints, charts, or schematics, to determine machine settings or adjustments. | Reassemble machines after making repairs or replacing parts. | Reinstall software programs or adjust settings on existing software to fix machine malfunctions. | Repair, adjust, or replace electrical or mechanical components or parts, using hand tools, power tools, or soldering or welding equipment. | Test components or circuits of faulty equipment to locate defects, using oscilloscopes, signal generators, ammeters, voltmeters, or special diagnostic software programs. | Test new systems to ensure that they are in working order. | Train new repairers. | Travel to customers' stores or offices to service machines or to provide emergency repair service. | Update existing equipment, performing tasks such as installing updated circuit boards or additional memory.</t>
+  </si>
+  <si>
+    <t>49-2021.00</t>
+  </si>
+  <si>
+    <t>Radio, Cellular, and Tower Equipment Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Communications Systems Technician | Field Service Technician (Field Service Tech) | Field Technician (Field Tech) | Installation Technician (Installation Tech) | Radio Frequency Technician (RF Tech) | Radio Repairman | Radio Technician (Radio Tech) | Tower Technician (Tower Tech) | Two-Way Radio Technician (Two-Way Radio Tech)</t>
+  </si>
+  <si>
+    <t>AERONET calculator | Backbone.js | Caliper Maptitude | Computerized maintenance management system CMMS | Location mapping software | Maintenance documentation software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Sweep analysis software | Zoho WebNMS Cell Tower Manager</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Telecommunications | Customer and Personal Service | Mechanical | Administration and Management | Engineering and Technology | English Language | Public Safety and Security | Mathematics | Communications and Media</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Arm-Hand Steadiness | Information Ordering | Deductive Reasoning | Finger Dexterity | Speech Recognition | Oral Comprehension | Manual Dexterity | Perceptual Speed | Category Flexibility | Inductive Reasoning | Oral Expression | Written Comprehension | Speech Clarity | Extent Flexibility | Control Precision | Far Vision | Selective Attention | Visualization | Written Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Telephone Conversations | E-Mail | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Frequency of Decision Making | Deal With External Customers or the Public in General | Consequence of Error | Outdoors, Exposed to All Weather Conditions | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Audiovisual Equipment Installers and Repairers | Avionics Technicians | Broadcast Technicians | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Lighting Technicians | Power Distributors and Dispatchers | Radio Frequency Identification Device Specialists | Security and Fire Alarm Systems Installers | Signal and Track Switch Repairers | Telecommunications Engineering Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Repair, install, or maintain mobile or stationary radio transmitting, broadcasting, and receiving equipment, and two-way radio communications systems used in cellular telecommunications, mobile broadband, ship-to-shore, aircraft-to-ground communications, and radio equipment in service and emergency vehicles. May test and analyze network coverage.</t>
+  </si>
+  <si>
+    <t>Bolt equipment into place, using hand or power tools. | Calibrate and align components, using scales, gauges, and other measuring instruments. | Check antenna positioning to ensure specified azimuths or mechanical tilts and adjust as necessary. | Climb communication towers to install, replace, or repair antennas or auxiliary equipment used to transmit and receive radio waves. | Climb towers to access components, using safety equipment, such as full-body harnesses. | Complete reports related to project status, progress, or other work details, using computer software. | Examine malfunctioning radio equipment to locate defects such as loose connections, broken wires, or burned-out components, using schematic diagrams and test equipment. | Insert plugs into receptacles and bolt or screw leads to terminals to connect equipment to power sources, using hand tools. | Inspect completed work to ensure all hardware is tight, antennas are level, hangers are properly fastened, proper support is in place, or adequate weather proofing has been installed. | Install all necessary transmission equipment components, including antennas or antenna mounts, surge arrestors, transmission lines, connectors, or tower-mounted amplifiers (TMAs). | Install or repair tower lighting components, including strobes, beacons, or lighting controllers. | Install, adjust, and repair stationary and mobile radio transmitting and receiving equipment and two-way radio communication systems. | Install, connect, or test underground or aboveground grounding systems. | Lift equipment into position, using cranes and rigging tools or equipment, such as gin poles. | Locate tower sites where work is to be performed, using mapping software. | Monitor radio range stations to detect transmission flaws and adjust controls to eliminate flaws. | Mount equipment on transmission towers and in vehicles such as ships or ambulances. | Perform maintenance or repair work on existing tower equipment, using hand or power tools. | Read work orders, blueprints, plans, datasheets or site drawings to determine work to be done. | Remove and replace defective components and parts such as conductors, resistors, semiconductors, and integrated circuits, using soldering irons, wire cutters, and hand tools. | Repair circuits, wiring, and soldering, using soldering irons and hand tools to install parts and adjust connections. | Replace existing antennas with new antennas as directed. | Run appropriate power, ground, or coaxial cables. | Take site survey photos or photos of work performed, using digital cameras. | Test batteries, using hydrometers and ammeters, and charge batteries as necessary. | Test emergency transmitters to ensure their readiness for immediate use. | Test equipment functions such as signal strength and quality, transmission capacity, interference, and signal delay, using equipment such as oscilloscopes, circuit analyzers, frequency meters, and wattmeters. | Test operation of tower transmission components, using sweep testing tools or software. | Transport equipment to work sites, using utility trucks and equipment trailers. | Turn setscrews to adjust receivers for maximum sensitivity and transmitters for maximum output.</t>
+  </si>
+  <si>
+    <t>49-2022.00</t>
+  </si>
+  <si>
+    <t>Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Broadband Technician | Central Office Technician | Combination Technician | Customer Service Technician (CST) | Field Technician | Install and Repair Technician | Installer | Outside Plant Technician | Service Technician | Telecommunications Technician</t>
+  </si>
+  <si>
+    <t>Apache Struts | Autodesk AutoCAD | Cisco IOS | Firewall software | Fluke ClearSight Analyzer | Fluke Networks Fluke TechEXPERT | Fluke Networks TechAdvisor Field Access System | Geographic information system GIS systems | IBM Domino | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Supervisory control and data acquisition SCADA software | Voice over internet protocol VoIP system software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Monitoring | Speaking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Telecommunications | Computers and Electronics | English Language | Mathematics | Public Safety and Security | Mechanical | Engineering and Technology | Education and Training</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Near Vision | Visual Color Discrimination | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Information Ordering | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Speech Recognition | Multilimb Coordination | Oral Expression | Flexibility of Closure | Far Vision | Perceptual Speed | Visualization | Control Precision | Category Flexibility | Written Comprehension | Extent Flexibility | Selective Attention | Auditory Attention | Depth Perception | Gross Body Equilibrium | Gross Body Coordination | Trunk Strength | Static Strength | Speed of Closure | Fluency of Ideas | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | In an Enclosed Vehicle or Operate Enclosed Equipment | Telephone Conversations | Frequency of Decision Making | Contact With Others | Freedom to Make Decisions | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Exposed to Extremely Bright or Inadequate Lighting Conditions | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Cramped Work Space, Awkward Positions | Spend Time Standing</t>
+  </si>
+  <si>
+    <t>Audiovisual Equipment Installers and Repairers | Avionics Technicians | Broadcast Technicians | Computer Network Architects | Computer Network Support Specialists | Computer, Automated Teller, and Office Machine Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Network and Computer Systems Administrators | Power Distributors and Dispatchers | Radio, Cellular, and Tower Equipment Installers and Repairers | Security and Fire Alarm Systems Installers | Signal and Track Switch Repairers | Telecommunications Engineering Specialists | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Install, set up, rearrange, or remove switching, distribution, routing, and dialing equipment used in central offices or headends. Service or repair telephone, cable television, Internet, and other communications equipment on customers' property. May install communications equipment or communications wiring in buildings.</t>
+  </si>
+  <si>
+    <t>Address special issues or situations, such as illegal or unauthorized use of equipment, or cases of electrical or acoustic shock. | Adjust or modify equipment to enhance equipment performance or to respond to customer requests. | Analyze test readings, computer printouts, and trouble reports to determine equipment repair needs and required repair methods. | Assemble and install communication equipment such as data and telephone communication lines, wiring, switching equipment, wiring frames, power apparatus, computer systems, and networks. | Clean and maintain tools, test equipment, and motor vehicles. | Clean switches and replace contact points, using vacuum hoses, solvents, and hand tools. | Climb poles and ladders, use truck-mounted booms, and enter areas such as manholes and cable vaults to install, maintain, or inspect equipment. | Collaborate with other workers to locate and correct malfunctions. | Communicate with bases, using telephones or two-way radios to receive instructions or technical advice, or to report equipment status. | Demonstrate equipment to customers and explain its use, responding to any inquiries or complaints. | Designate cables available for use. | Determine viability of sites through observation, and discuss site locations and construction requirements with customers. | Diagnose and correct problems from remote locations, using special switchboards to find the sources of problems. | Dig holes or trenches as necessary for equipment installation and access. | Drive crew trucks to and from work areas. | Enter codes needed to correct electronic switching system programming. | Examine telephone transmission facilities to determine requirements for new or additional telephone services. | Inspect equipment on a regular basis to ensure proper functioning. | Install telephone station equipment, such as intercommunication systems, transmitters, receivers, relays, and ringers, and related apparatus, such as coin collectors, telephone booths, and switching-key equipment. | Install updated software and programs that maintain existing software or provide requested features, such as time-correlated call routing. | Maintain computer and manual records pertaining to facilities and equipment. | Measure distances from landmarks to identify exact installation sites for equipment. | Note differences in wire and cable colors so that work can be performed correctly. | Perform database verifications, using computers. | Perform routine maintenance on equipment, including adjusting and lubricating components and painting worn or exposed areas. | Program computerized switches and switchboards to provide requested features. | Provide input into the design and manufacturing of new equipment. | Refer to manufacturers' manuals to obtain maintenance instructions pertaining to specific malfunctions. | Remove and remake connections to change circuit layouts, following work orders or diagrams. | Remove and replace plug-in circuit equipment. | Remove loose wires and other debris after work is completed. | Repair or replace faulty equipment, such as defective and damaged telephones, wires, switching system components, and associated equipment. | Request support from technical service centers when on-site procedures fail to solve installation or maintenance problems. | Review manufacturer's instructions, manuals, technical specifications, building permits, and ordinances to determine communication equipment requirements and procedures. | Route and connect cables and lines to switches, switchboard equipment, and distributing frames, using wire-wrap guns or soldering irons to connect wires to terminals. | Run wires between components and to outside cable systems, connecting them to wires from telephone poles or underground cable accesses. | Test circuits and components of malfunctioning telecommunications equipment to isolate sources of malfunctions, using test meters, circuit diagrams, polarity probes, and other hand tools. | Test connections to ensure that power supplies are adequate and that communications links function. | Test repaired, newly installed, or updated equipment to ensure that it functions properly and conforms to specifications, using test equipment and observation.</t>
+  </si>
+  <si>
+    <t>49-2091.00</t>
+  </si>
+  <si>
+    <t>Avionics Technicians</t>
+  </si>
+  <si>
+    <t>Aircraft Electrical Systems Specialist | Aircraft Technician | Aviation Electrical Technician | Aviation Electronics Technician | Avionics Electronics Technician | Avionics Installer | Avionics Systems Integration Specialist | Avionics Technician (Avionics Tech) | Electronic Technician</t>
+  </si>
+  <si>
+    <t>Apache HTTP Server | Autodesk AutoCAD | Avionics system testing software | C++ | Computer diagnostic software | Dassault Systemes CATIA | Linux | Maintenance record software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Java | SAP software | Software development tools | Technical Data Management System TDMS | UNIX | Workday software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension | Writing | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Mechanical | English Language | Engineering and Technology | Customer and Personal Service | Telecommunications | Design | Mathematics | Education and Training | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Written Comprehension | Oral Comprehension | Problem Sensitivity | Information Ordering | Near Vision | Written Expression | Deductive Reasoning | Inductive Reasoning | Finger Dexterity | Oral Expression | Control Precision | Arm-Hand Steadiness | Visualization | Manual Dexterity | Speech Clarity | Speech Recognition | Visual Color Discrimination | Selective Attention | Perceptual Speed | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Impact of Decisions on Co-workers or Company Results | Indoors, Environmentally Controlled | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | E-Mail | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Telephone Conversations | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Consequence of Error | Exposed to Contaminants | Exposed to Hazardous Conditions</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Aircraft Mechanics and Service Technicians | Aircraft Service Attendants | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Engineering Technicians | Calibration Technologists and Technicians | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Engine and Other Machine Assemblers | Lighting Technicians | Mechanical Engineers | Robotics Technicians</t>
+  </si>
+  <si>
+    <t>Install, inspect, test, adjust, or repair avionics equipment, such as radar, radio, navigation, and missile control systems in aircraft or space vehicles.</t>
+  </si>
+  <si>
+    <t>Adjust, repair, or replace malfunctioning components or assemblies, using hand tools or soldering irons. | Assemble components such as switches, electrical controls, and junction boxes, using hand tools or soldering irons. | Assemble prototypes or models of circuits, instruments, and systems for use in testing. | Connect components to assemblies such as radio systems, instruments, magnetos, inverters, and in-flight refueling systems, using hand tools and soldering irons. | Coordinate work with that of engineers, technicians, and other aircraft maintenance personnel. | Fabricate parts and test aids as required. | Install electrical and electronic components, assemblies, and systems in aircraft, using hand tools, power tools, or soldering irons. | Interpret flight test data to diagnose malfunctions and systemic performance problems. | Keep records of maintenance and repair work. | Lay out installation of aircraft assemblies and systems, following documentation such as blueprints, manuals, and wiring diagrams. | Operate computer-aided drafting and design applications to design avionics system modifications. | Set up and operate ground support and test equipment to perform functional flight tests of electrical and electronic systems. | Test and troubleshoot instruments, components, and assemblies, using circuit testers, oscilloscopes, or voltmeters.</t>
+  </si>
+  <si>
+    <t>49-2092.00</t>
+  </si>
+  <si>
+    <t>Electric Motor, Power Tool, and Related Repairers</t>
+  </si>
+  <si>
+    <t>Electric Motor Mechanic | Electric Motor Repairman | Electric Motor Winder | Electro Mechanic | Maintenance Technician | Power Tool Repair Technician | Repair Technician | Service Technician | Tool Repair Technician | Tool Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Commutator profiling software | Computerized maintenance management system CMMS | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Motor testing software | Python | SAP software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | English Language | Administration and Management | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Problem Sensitivity | Near Vision | Manual Dexterity | Arm-Hand Steadiness | Information Ordering | Visualization | Visual Color Discrimination | Deductive Reasoning | Hearing Sensitivity | Inductive Reasoning | Written Comprehension | Oral Comprehension | Reaction Time | Multilimb Coordination | Control Precision | Perceptual Speed | Flexibility of Closure | Speed of Closure | Extent Flexibility | Rate Control | Selective Attention | Category Flexibility | Auditory Attention | Depth Perception | Oral Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Importance of Being Exact or Accurate | Spend Time Standing | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Time Pressure | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Contact With Others | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Hazardous Conditions | Exposed to Minor Burns, Cuts, Bites, or Stings | Telephone Conversations | Spend Time Making Repetitive Motions | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Coil Winders, Tapers, and Finishers | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Helpers--Installation, Maintenance, and Repair Workers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Timing Device Assemblers and Adjusters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Repair, maintain, or install electric motors, wiring, or switches.</t>
+  </si>
+  <si>
+    <t>Adjust working parts, such as fan belts, contacts, and springs, using hand tools and gauges. | Assemble electrical parts such as alternators, generators, starting devices, and switches, following schematic drawings and using hand, machine, and power tools. | Clean cells, cell assemblies, glassware, leads, electrical connections, and battery poles, using scrapers, steam, water, emery cloths, power grinders, or acid. | Cut and form insulation, and insert insulation into armature, rotor, or stator slots. | Disassemble defective equipment so that repairs can be made, using hand tools. | Hammer out dents and twists in tools and equipment. | Inspect and test equipment to locate damage or worn parts and diagnose malfunctions, or read work orders or schematic drawings to determine required repairs. | Inspect electrical connections, wiring, relays, charging resistance boxes, and storage batteries, following wiring diagrams. | Lift units or parts such as motors or generators, using cranes or chain hoists, or signal crane operators to lift heavy parts or subassemblies. | Lubricate moving parts. | Maintain stocks of parts. | Measure velocity, horsepower, revolutions per minute (rpm), amperage, circuitry, and voltage of units or parts to diagnose problems, using ammeters, voltmeters, wattmeters, and other testing devices. | Read service guides to find information needed to perform repairs. | Reassemble repaired electric motors to specified requirements and ratings, using hand tools and electrical meters. | Record repairs required, parts used, and labor time. | Reface, ream, and polish commutators and machine parts to specified tolerances, using machine tools. | Remove and replace defective parts such as coil leads, carbon brushes, and wires, using soldering equipment. | Repair and operate battery-charging equipment. | Repair and rebuild defective mechanical parts in electric motors, generators, and related equipment, using hand tools and power tools. | Rewind coils on cores in slots, or make replacement coils, using coil-winding machines. | Rewire electrical systems, and repair or replace electrical accessories. | Scrape and clean units or parts, using cleaning solvents and equipment such as buffing wheels. | Seal joints with putty, mortar, and asbestos, using putty extruders and knives. | Set machinery for proper performance, using computers. | Sharpen tools such as saws, picks, shovels, screwdrivers, and scoops, either manually or by using bench grinders and emery wheels. | Solder, wrap, and coat wires to ensure proper insulation. | Steam-clean polishing and buffing wheels to remove abrasives and bonding materials, and spray, brush, or recoat surfaces as necessary. | Test battery charges, and replace or recharge batteries as necessary. | Test equipment for overheating, using speed gauges and thermometers. | Verify and adjust alignments and dimensions of parts, using gauges and tracing lathes. | Weld, braze, or solder electrical connections.</t>
+  </si>
+  <si>
+    <t>49-2093.00</t>
+  </si>
+  <si>
+    <t>Electrical and Electronics Installers and Repairers, Transportation Equipment</t>
+  </si>
+  <si>
+    <t>Critical Systems Technician | Electronic Bench Technician | Electronics Mechanic | Locomotive Electrician | Power Technician (Power Tech) | Ship Yard Electrical Person</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk Revit | Fluke Corporation FlukeView Forms | IBM Lotus 1-2-3 | IBM Lotus Notes | Linux | Megger PowerDB | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Trimble SketchUp Pro</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Monitoring | Reading Comprehension | Speaking | Writing</t>
+  </si>
+  <si>
+    <t>Engineering and Technology | Computers and Electronics | Mathematics | Public Safety and Security | Mechanical | Design | English Language | Telecommunications | Education and Training | Customer and Personal Service | Production and Processing | Transportation | Physics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Problem Sensitivity | Manual Dexterity | Visual Color Discrimination | Finger Dexterity | Oral Comprehension | Information Ordering | Control Precision | Multilimb Coordination | Extent Flexibility | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Far Vision | Selective Attention | Visualization | Category Flexibility | Oral Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Spend Time Making Repetitive Motions | Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Determine Tasks, Priorities and Goals | Exposed to Cramped Work Space, Awkward Positions | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Spend Time Kneeling, Crouching, Stooping, or Crawling | Indoors, Environmentally Controlled | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Bending or Twisting Your Body | Freedom to Make Decisions | Consequence of Error | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Avionics Technicians | Calibration Technologists and Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Helpers--Electricians | Industrial Machinery Mechanics | Lighting Technicians | Maintenance and Repair Workers, General | Mechanical Engineering Technologists and Technicians | Millwrights | Robotics Technicians</t>
+  </si>
+  <si>
+    <t>Install, adjust, or maintain mobile electronics communication equipment, including sound, sonar, security, navigation, and surveillance systems on trains, watercraft, or other mobile equipment.</t>
+  </si>
+  <si>
+    <t>Adjust, repair, or replace defective wiring and relays in ignition, lighting, air-conditioning, and safety control systems, using electrician's tools. | Confer with customers to determine the nature of malfunctions. | Cut openings and drill holes for fixtures, outlet boxes, and fuse holders, using electric drills and routers. | Estimate costs of repairs based on parts and labor requirements. | Inspect and test electrical systems and equipment to locate and diagnose malfunctions, using visual inspections, testing devices, and computer software. | Install electrical equipment such as air-conditioning, heating, or ignition systems and components such as generator brushes and commutators, using hand tools. | Install fixtures, outlets, terminal boards, switches, and wall boxes, using hand tools. | Install new fuses, electrical cables, or power sources as required. | Locate and remove or repair circuit defects such as blown fuses or malfunctioning transistors. | Maintain equipment service records. | Measure, cut, and install frameworks and conduit to support and connect wiring, control panels, and junction boxes, using hand tools. | Reassemble and test equipment after repairs. | Refer to schematics and manufacturers' specifications that show connections and provide instructions on how to locate problems. | Repair or rebuild equipment such as starters, generators, distributors, or door controls, using electrician's tools. | Splice wires with knives or cutting pliers, and solder connections to fixtures, outlets, and equipment.</t>
+  </si>
+  <si>
+    <t>49-2094.00</t>
+  </si>
+  <si>
+    <t>Electrical and Electronics Repairers, Commercial and Industrial Equipment</t>
+  </si>
+  <si>
+    <t>Control Technician | E and I Mechanic (Electrical and Instrument Mechanic) | E and I Mechanic (Electrical and Instrumentation Mechanic) | Electrical Maintenance Technician | Electrical and Instrument Technician (E and I Tech) | Electronic Technician | I and C Tech (Instrument and Control Technician) | Instrument and Electrical Technician (I and E Tech) | Repair Technician | Scale Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Circuit evaluation software | Computerized maintenance management system CMMS | Database software | Email software | Maintenance management software | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word | Programmable logic controller PLC software | Rockwell RSLogix | SAP Maintenance</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Mechanical | Production and Processing | Customer and Personal Service | Mathematics | Administration and Management | Engineering and Technology | English Language | Design | Education and Training</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Information Ordering | Near Vision | Oral Comprehension | Deductive Reasoning | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Flexibility of Closure | Perceptual Speed | Visualization | Visual Color Discrimination | Oral Expression | Written Comprehension | Category Flexibility | Inductive Reasoning | Speech Clarity | Speech Recognition | Far Vision | Control Precision | Selective Attention | Originality | Fluency of Ideas | Written Expression</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | E-Mail | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Exposed to Hazardous Equipment | Spend Time Standing | Physical Proximity | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Avionics Technicians | Calibration Technologists and Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Electronics Engineers, Except Computer | Industrial Machinery Mechanics | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Mechatronics Engineers | Medical Equipment Repairers | Robotics Technicians</t>
+  </si>
+  <si>
+    <t>Repair, test, adjust, or install electronic equipment, such as industrial controls, transmitters, and antennas.</t>
+  </si>
+  <si>
+    <t>Advise management regarding customer satisfaction, product performance, or suggestions for product improvements. | Calibrate testing instruments and installed or repaired equipment to prescribed specifications. | Consult with customers, supervisors, or engineers to plan layout of equipment or to resolve problems in system operation or maintenance. | Coordinate efforts with other workers involved in installing or maintaining equipment or components. | Determine feasibility of using standardized equipment or develop specifications for equipment required to perform additional functions. | Develop or modify industrial electronic devices, circuits, or equipment, according to available specifications. | Enter information into computer to copy program or to draw, modify, or store schematics, applying knowledge of software package used. | Examine work orders and converse with equipment operators to detect equipment problems and to ascertain whether mechanical or human errors contributed to the problems. | Inspect components of industrial equipment for accurate assembly and installation or for defects, such as loose connections or frayed wires. | Install repaired equipment in various settings, such as industrial or military establishments. | Maintain equipment logs that record performance problems, repairs, calibrations, or tests. | Maintain inventory of spare parts. | Operate equipment to demonstrate proper use or to analyze malfunctions. | Perform scheduled preventive maintenance tasks, such as checking, cleaning, or repairing equipment, to detect and prevent problems. | Repair or adjust equipment, machines, or defective components, replacing worn parts, such as gaskets or seals in watertight electrical equipment. | Send defective units to the manufacturer or to a specialized repair shop for repair. | Set up and test industrial equipment to ensure that it functions properly. | Sign overhaul documents for equipment replaced or repaired. | Study blueprints, schematics, manuals, or other specifications to determine installation procedures. | Test faulty equipment to diagnose malfunctions, using test equipment or software, and applying knowledge of the functional operation of electronic units and systems.</t>
+  </si>
+  <si>
+    <t>49-2095.00</t>
+  </si>
+  <si>
+    <t>Electrical and Electronics Repairers, Powerhouse, Substation, and Relay</t>
+  </si>
+  <si>
+    <t>Electrical Technician | Electrical and Instrumentation Technician (E and I Technician) | Instrument and Control Technician (I and C Technician) | Instrumentation and Control Technician (I and C Technician) | Relay Technician | Substation Electrician | Substation Mechanic | Substation Technician | Substation Wireman | Wireman</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Fluke Corporation FlukeView Forms | Megger PowerDB | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | OMICRON Test Universe | Supervisory control and data acquisition SCADA software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Speaking | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Engineering and Technology | Public Safety and Security | English Language | Computers and Electronics | Design | Physics | Building and Construction | Education and Training</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Oral Comprehension | Problem Sensitivity | Written Comprehension | Oral Expression | Information Ordering | Finger Dexterity | Control Precision | Visual Color Discrimination | Manual Dexterity | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Written Expression | Far Vision | Selective Attention | Visualization | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Health and Safety of Other Workers | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | E-Mail | Impact of Decisions on Co-workers or Company Results | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Conditions | Exposed to Very Hot or Cold Temperatures | Importance of Repeating Same Tasks | Time Pressure | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Not Environmentally Controlled | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Indoors, Environmentally Controlled | Spend Time Standing | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Exposed to High Places | Outdoors, Under Cover | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Engineers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electricians | Electromechanical Equipment Assemblers | Electronics Engineers, Except Computer | Geothermal Technicians | Hydroelectric Plant Technicians | Industrial Machinery Mechanics | Lighting Technicians | Power Distributors and Dispatchers | Robotics Technicians | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Inspect, test, repair, or maintain electrical equipment in generating stations, substations, and in-service relays.</t>
+  </si>
+  <si>
+    <t>Analyze test data to diagnose malfunctions, to determine performance characteristics of systems, or to evaluate effects of system modifications. | Construct, test, maintain, and repair substation relay and control systems. | Consult manuals, schematics, wiring diagrams, and engineering personnel to troubleshoot and solve equipment problems and to determine optimum equipment functioning. | Disconnect voltage regulators, bolts, and screws, and connect replacement regulators to high-voltage lines. | Inspect and test equipment and circuits to identify malfunctions or defects, using wiring diagrams and testing devices such as ohmmeters, voltmeters, or ammeters. | Maintain inventories of spare parts for all equipment, requisitioning parts as necessary. | Notify facility personnel of equipment shutdowns. | Open and close switches to isolate defective relays, performing adjustments or repairs. | Prepare and maintain records detailing tests, repairs, and maintenance. | Repair, replace, and clean equipment and components such as circuit breakers, brushes, and commutators. | Run signal quality and connectivity tests for individual cables, and record results. | Schedule and supervise splicing or termination of cables in color-code order. | Schedule and supervise the construction and testing of special devices and the implementation of unique monitoring or control systems. | Test insulators and bushings of equipment by inducing voltage across insulation, testing current, and calculating insulation loss. | Test oil in circuit breakers and transformers for dielectric strength, refilling oil periodically.</t>
+  </si>
+  <si>
+    <t>49-2096.00</t>
+  </si>
+  <si>
+    <t>Electronic Equipment Installers and Repairers, Motor Vehicles</t>
+  </si>
+  <si>
+    <t>Automotive Technician | Car Audio Installer | Car Electronics Installer | Car Stereo Installer | Electronic Equipment Installer | Electronic Technician | Installation Technician | Installer | Mobile Electronics Installation Specialist | Mobile Electronics Installer</t>
+  </si>
+  <si>
+    <t>Harris Tech X.over Pro | Harris Technologies BassBox | Installalogy Access Client | LinearTeam WinISD | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | MobileToys MAIDXL | True Audio WinSpeakerz | WHE Term-PAK</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Computers and Electronics | Customer and Personal Service | Mathematics | English Language | Engineering and Technology | Education and Training</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Finger Dexterity | Near Vision | Visual Color Discrimination | Problem Sensitivity | Deductive Reasoning | Visualization | Extent Flexibility | Inductive Reasoning | Oral Comprehension | Manual Dexterity | Selective Attention | Control Precision | Oral Expression | Information Ordering | Multilimb Coordination | Category Flexibility | Written Comprehension | Trunk Strength | Speech Clarity | Speech Recognition | Auditory Attention | Hearing Sensitivity | Time Sharing | Flexibility of Closure | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Spend Time Standing | Frequency of Decision Making | Spend Time Making Repetitive Motions | Indoors, Not Environmentally Controlled | Determine Tasks, Priorities and Goals | Exposed to Cramped Work Space, Awkward Positions | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Spend Time Bending or Twisting Your Body | Contact With Others</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Audiovisual Equipment Installers and Repairers | Automotive Engineering Technicians | Automotive Service Technicians and Mechanics | Avionics Technicians | Calibration Technologists and Technicians | Computer, Automated Teller, and Office Machine Repairers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Electronics Engineers, Except Computer | Engine and Other Machine Assemblers | Lighting Technicians | Radio, Cellular, and Tower Equipment Installers and Repairers | Security and Fire Alarm Systems Installers | Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Install, diagnose, or repair communications, sound, security, or navigation equipment in motor vehicles.</t>
+  </si>
+  <si>
+    <t>Build fiberglass or wooden enclosures for sound components, and fit them to automobile dimensions. | Confer with customers to determine the nature of malfunctions. | Cut openings and drill holes for fixtures and equipment, using electric drills and routers. | Diagnose or repair problems with electronic equipment, such as sound, navigation, communication, and security equipment, in motor vehicles. | Estimate costs of repairs, based on parts and labor charges. | Inspect and test electrical or electronic systems to locate and diagnose malfunctions, using visual inspections and testing instruments, such as oscilloscopes and voltmeters. | Install equipment and accessories, such as stereos, navigation equipment, communication equipment, and security systems. | Record results of diagnostic tests. | Remove seats, carpeting, and interiors of doors and add sound-absorbing material in empty spaces, reinstalling interior parts. | Replace and clean electrical or electronic components. | Run new speaker and electrical cables. | Splice wires with knives or cutting pliers, and solder connections to fixtures and equipment.</t>
+  </si>
+  <si>
+    <t>49-2097.00</t>
+  </si>
+  <si>
+    <t>Audiovisual Equipment Installers and Repairers</t>
+  </si>
+  <si>
+    <t>A/V Installation Tech (Audio Visual Installation Technician) | A/V Installer (Audio Visual Installer) | Electronic Tech (Electronic Technician) | Field Service Tech (Field Service Technician) | Home Theater Installer | Installer | Satellite Installer | TV Analyzer (Television Analyzer) | TV Repairman (Television Repairman)</t>
+  </si>
+  <si>
+    <t>Audio calibration software | Global positioning system GPS software | Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Speaking | Reading Comprehension | Active Listening | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Customer and Personal Service | Telecommunications | Mechanical | English Language | Engineering and Technology | Administration and Management | Building and Construction</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Near Vision | Visualization | Problem Sensitivity | Deductive Reasoning | Information Ordering | Manual Dexterity | Far Vision | Visual Color Discrimination | Oral Comprehension | Arm-Hand Steadiness | Category Flexibility | Inductive Reasoning | Oral Expression | Speech Clarity | Speech Recognition | Hearing Sensitivity | Control Precision | Selective Attention | Flexibility of Closure | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Time Pressure | Outdoors, Exposed to All Weather Conditions | Importance of Being Exact or Accurate | Physical Proximity | Contact With Others | Exposed to Contaminants | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Audio and Video Technicians | Avionics Technicians | Broadcast Technicians | Calibration Technologists and Technicians | Camera and Photographic Equipment Repairers | Computer, Automated Teller, and Office Machine Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Lighting Technicians | Motion Picture Projectionists | Radio Frequency Identification Device Specialists | Radio, Cellular, and Tower Equipment Installers and Repairers | Security and Fire Alarm Systems Installers | Telecommunications Engineering Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Install, repair, or adjust audio or television receivers, stereo systems, camcorders, video systems, or other electronic entertainment equipment in homes or other venues. May perform routine maintenance.</t>
+  </si>
+  <si>
+    <t>Calibrate and test equipment, and locate circuit and component faults, using hand and power tools and measuring and testing instruments such as resistance meters and oscilloscopes. | Compute cost estimates for labor and materials. | Confer with customers to determine the nature of problems or to explain repairs. | Disassemble entertainment equipment and repair or replace loose, worn, or defective components and wiring, using hand tools and soldering irons. | Install, service, and repair electronic equipment or instruments such as televisions, radios, and videocassette recorders. | Instruct customers on the safe and proper use of equipment. | Keep records of work orders and test and maintenance reports. | Make service calls to repair units in customers' homes, or return units to shops for major repairs. | Position or mount speakers, and wire speakers to consoles. | Read and interpret electronic circuit diagrams, function block diagrams, specifications, engineering drawings, and service manuals. | Tune or adjust equipment and instruments to obtain optimum visual or auditory reception, according to specifications, manuals, and drawings.</t>
+  </si>
+  <si>
+    <t>49-2098.00</t>
+  </si>
+  <si>
+    <t>Security and Fire Alarm Systems Installers</t>
+  </si>
+  <si>
+    <t>Alarm Technician | Fire Alarm Technician (Fire Alarm Tech) | Home Security Alarm Installer | Install Technician | Installation Technician | Installer | Security Installation Technician | Security Installer | Security Technician (Security Tech) | Service Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Exacq Technologies software | Microsoft Excel | Microsoft Hyperterminal | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Traceroute</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension | Monitoring</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Computers and Electronics | Customer and Personal Service | Telecommunications | Building and Construction | Engineering and Technology | English Language | Mechanical | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Near Vision | Deductive Reasoning | Manual Dexterity | Arm-Hand Steadiness | Information Ordering | Inductive Reasoning | Visualization | Category Flexibility | Speech Clarity | Speech Recognition | Extent Flexibility | Multilimb Coordination | Finger Dexterity | Far Vision | Control Precision | Perceptual Speed | Written Expression | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Frequency of Decision Making | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Spend Time Standing | In an Enclosed Vehicle or Operate Enclosed Equipment | Deal With External Customers or the Public in General | E-Mail | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Work With or Contribute to a Work Group or Team | Indoors, Not Environmentally Controlled | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Consequence of Error | Written Letters and Memos | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Audiovisual Equipment Installers and Repairers | Avionics Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electricians | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Electronics Engineers, Except Computer | Fire-Prevention and Protection Engineers | Lighting Technicians | Maintenance and Repair Workers, General | Penetration Testers | Power Distributors and Dispatchers | Radio, Cellular, and Tower Equipment Installers and Repairers | Security Management Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Install, program, maintain, and repair security and fire alarm wiring and equipment. Ensure that work is in accordance with relevant codes.</t>
+  </si>
+  <si>
+    <t>Adjust sensitivity of units, based on room structures and manufacturers' recommendations, using programming keypads. | Consult with clients to assess risks and to determine security requirements. | Demonstrate systems for customers and explain details, such as the causes and consequences of false alarms. | Drill holes for wiring in wall studs, joists, ceilings, or floors. | Examine systems to locate problems, such as loose connections or broken insulation. | Feed cables through access holes, roof spaces, or cavity walls to reach fixture outlets, positioning and terminating cables, wires, or strapping. | Inspect installation sites and study work orders, building plans, and installation manuals to determine materials requirements and installation procedures. | Install, maintain, or repair security systems, alarm devices, or related equipment, following blueprints of electrical layouts and building plans. | Keep informed of new products and developments. | Mount and fasten control panels, door and window contacts, sensors, or video cameras, and attach electrical and telephone wiring to connect components. | Mount raceways and conduits and fasten wires to wood framing, using staplers. | Order replacement parts. | Prepare documents, such as invoices or warranties. | Provide customers with cost estimates for equipment installation. | Test and repair circuits and sensors, following wiring and system specifications. | Test backup batteries, keypad programming, sirens, or other security features to ensure proper functioning or to diagnose malfunctions.</t>
+  </si>
+  <si>
+    <t>49-3011.00</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians</t>
+  </si>
+  <si>
+    <t>Aircraft Maintainer | Aircraft Maintenance Technician (Aircraft Maintenance Tech) | Aircraft Mechanic | Aircraft Restorer | Aircraft Service Technician (Aircraft Service Tech) | Aircraft Technician (Aircraft Tech) | Airframe and Powerplant Mechanic (A and P Mechanic) | Aviation Maintenance Technician (AMT) | Aviation Mechanic | Helicopter Mechanic</t>
+  </si>
+  <si>
+    <t>Access Software AIRPAX | CaseBank SpotLight | Computerized aircraft log manager CALM | DatcoMedia EBis | Disassembler software | Engine analysis software | Maintenance information databases | Maintenance planning software | Maintenance record software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mxi Technologies Maintenix | Operational Data Store ODS software | Pentagon 2000SQL | SAP software | Supply system software | Technical Data Management System TDMS | Technical manual database software | Tracware AeroTrac | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Engineering and Technology | English Language | Transportation | Education and Training | Mathematics | Physics | Computers and Electronics | Design</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Written Comprehension | Information Ordering | Manual Dexterity | Finger Dexterity | Control Precision | Deductive Reasoning | Inductive Reasoning | Multilimb Coordination | Flexibility of Closure | Arm-Hand Steadiness | Oral Expression | Oral Comprehension | Hearing Sensitivity | Visualization | Visual Color Discrimination | Far Vision | Perceptual Speed | Trunk Strength | Written Expression | Category Flexibility | Selective Attention | Extent Flexibility | Speech Clarity | Auditory Attention | Speech Recognition | Depth Perception | Static Strength | Reaction Time | Response Orientation | Speed of Closure</t>
+  </si>
+  <si>
+    <t>Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Exposed to Contaminants | Contact With Others | Impact of Decisions on Co-workers or Company Results | Time Pressure | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Physical Proximity | Freedom to Make Decisions | Exposed to Hazardous Conditions | Exposed to Cramped Work Space, Awkward Positions | E-Mail | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Hazardous Equipment | Spend Time Walking or Running | Spend Time Making Repetitive Motions | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Aircraft Service Attendants | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Rail Car Repairers | Ship Engineers | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul aircraft engines and assemblies, such as hydraulic and pneumatic systems.</t>
+  </si>
+  <si>
+    <t>Accompany aircraft on flights to make in-flight adjustments and corrections. | Assemble and install electrical, plumbing, mechanical, hydraulic, and structural components and accessories, using hand or power tools. | Check for corrosion, distortion, and invisible cracks in the fuselage, wings, and tail, using x-ray and magnetic inspection equipment. | Clean engines, sediment bulk and screens, and carburetors, adjusting carburetor float levels. | Clean, refuel, and change oil in line service aircraft. | Clean, strip, prime, and sand structural surfaces and materials to prepare them for bonding. | Communicate with other workers to coordinate fitting and alignment of heavy parts, or to facilitate processing of repair parts. | Conduct routine and special inspections as required by regulations. | Cure bonded structures, using portable or stationary curing equipment. | Determine repair limits for engine hot section parts. | Disassemble engines and inspect parts, such as turbine blades or cylinders, for corrosion, wear, warping, cracks, and leaks, using precision measuring instruments, x-rays, and magnetic inspection equipment. | Examine and inspect aircraft components, including landing gear, hydraulic systems, and deicers to locate cracks, breaks, leaks, or other problems. | Examine engines through specially designed openings while working from ladders or scaffolds, or use hoists or lifts to remove the entire engine from an aircraft. | Fabricate defective sections or parts, using metal fabricating machines, saws, brakes, shears, and grinders. | Inspect airframes for wear or other defects. | Inspect completed work to certify that maintenance meets standards and that aircraft are ready for operation. | Install and align repaired or replacement parts for subsequent riveting or welding, using clamps and wrenches. | Inventory and requisition or order supplies, parts, materials, and equipment. | Listen to operating engines to detect and diagnose malfunctions, such as sticking or burned valves. | Locate and mark dimensions and reference lines on defective or replacement parts, using templates, scribes, compasses, and steel rules. | Maintain repair logs, documenting all preventive and corrective aircraft maintenance. | Maintain, repair, and rebuild aircraft structures, functional components, and parts, such as wings and fuselage, rigging, hydraulic units, oxygen systems, fuel systems, electrical systems, gaskets, or seals. | Measure parts for wear, using precision instruments. | Measure the tension of control cables. | Modify aircraft structures, space vehicles, systems, or components, following drawings, schematics, charts, engineering orders, and technical publications. | Obtain fuel and oil samples and check them for contamination. | Prepare and paint aircraft surfaces. | Read and interpret maintenance manuals, service bulletins, and other specifications to determine the feasibility and method of repairing or replacing malfunctioning or damaged components. | Read and interpret pilots' descriptions of problems to diagnose causes. | Reassemble engines following repair or inspection and reinstall engines in aircraft. | Remove or cut out defective parts or drill holes to gain access to internal defects or damage, using drills and punches. | Remove or install aircraft engines, using hoists or forklift trucks. | Remove, inspect, repair, and install in-flight refueling stores and external fuel tanks. | Replace or repair worn, defective, or damaged components, using hand tools, gauges, and testing equipment. | Service and maintain aircraft and related apparatus by performing activities such as flushing crankcases, cleaning screens, and or moving parts. | Spread plastic film over areas to be repaired to prevent damage to surrounding areas. | Test operation of engines and other systems, using test equipment, such as ignition analyzers, compression checkers, distributor timers, or ammeters. | Trim and shape replacement body sections to specified sizes and fits and secure sections in place, using adhesives, hand tools, and power tools.</t>
+  </si>
+  <si>
+    <t>49-3021.00</t>
+  </si>
+  <si>
+    <t>Automotive Body and Related Repairers</t>
+  </si>
+  <si>
+    <t>Auto Body Man | Auto Body Repair Technician (Auto Body Repair Tech) | Auto Body Repairman | Automotive Body Technician (Auto Body Tech) | Body Man | Body Technician (Body Tech) | Collision Repair Technician (Collision Repair Tech) | Collision Technician (Collision Tech) | Frame Man | Refinish Technician (Refinish Tech)</t>
+  </si>
+  <si>
+    <t>Accounts receivable software | Appointment scheduling software | AutoZone ALLDATA | Automotive and Accounting Software by R*KOM Invoice Writer | Collision damage estimation software | Collision damage measurement software | Equipment management information software | Materials management software | Microsoft Excel | Microsoft Office software | Microsoft OneNote | Microsoft Outlook | Microsoft Windows | Microsoft Word | Paint mixing and matching software | Swan River Estimiser Pro</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Visualization | Oral Comprehension | Problem Sensitivity | Information Ordering | Finger Dexterity | Near Vision | Visual Color Discrimination | Speech Recognition | Multilimb Coordination | Control Precision | Selective Attention | Category Flexibility | Oral Expression | Auditory Attention | Extent Flexibility | Trunk Strength | Static Strength | Flexibility of Closure | Written Comprehension | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Exposed to Hazardous Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Spend Time Standing | Freedom to Make Decisions | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Spend Time Kneeling, Crouching, Stooping, or Crawling | Impact of Decisions on Co-workers or Company Results | In an Enclosed Vehicle or Operate Enclosed Equipment | Level of Competition | Health and Safety of Other Workers | Contact With Others | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Glass Installers and Repairers | Automotive Service Technicians and Mechanics | Bus and Truck Mechanics and Diesel Engine Specialists | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Furniture Finishers | Grinding and Polishing Workers, Hand | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Molders, Shapers, and Casters, Except Metal and Plastic | Motorcycle Mechanics | Rail Car Repairers | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Tire Builders | Tire Repairers and Changers | Upholsterers</t>
+  </si>
+  <si>
+    <t>Repair and refinish automotive vehicle bodies and straighten vehicle frames.</t>
+  </si>
+  <si>
+    <t>Adjust or align headlights, wheels, and brake systems. | Apply heat to plastic panels, using hot-air welding guns or immersion in hot water, and press the softened panels back into shape by hand. | Chain or clamp frames and sections to alignment machines that use hydraulic pressure to align damaged components. | Clean work areas, using air hoses, to remove damaged material and discarded fiberglass strips used in repair procedures. | Cut and tape plastic separating film to outside repair areas to avoid damaging surrounding surfaces during repair procedure and remove tape and wash surfaces after repairs are complete. | Cut openings in vehicle bodies for the installation of customized windows, using templates and power shears or chisels. | File, grind, sand, and smooth filled or repaired surfaces, using power tools and hand tools. | Fill small dents that cannot be worked out with plastic or solder. | Fit and secure windows, vinyl roofs, and metal trim to vehicle bodies, using caulking guns, adhesive brushes, and mallets. | Fit and weld replacement parts into place, using wrenches and welding equipment, and grind down welds to smooth them, using power grinders and other tools. | Follow supervisors' instructions as to which parts to restore or replace and how much time the job should take. | Inspect repaired vehicles for proper functioning, completion of work, dimensional accuracy, and overall appearance of paint job, and test-drive vehicles to ensure proper alignment and handling. | Measure and mark vinyl material and cut material to size for roof installation, using rules, straightedges, and hand shears. | Mix polyester resins and hardeners to be used in restoring damaged areas. | Position dolly blocks against surfaces of dented areas and beat opposite surfaces to remove dents, using hammers. | Prime and paint repaired surfaces, using paint sprayguns and motorized sanders. | Read specifications or confer with customers to determine the desired custom modifications for altering the appearance of vehicles. | Remove damaged panels, and identify the family and properties of the plastic used on a vehicle. | Remove damaged sections of vehicles using metal-cutting guns, air grinders and wrenches, and install replacement parts using wrenches or welding equipment. | Remove small pits and dimples in body metal, using pick hammers and punches. | Remove upholstery, accessories, electrical window-and-seat-operating equipment, and trim to gain access to vehicle bodies and fenders. | Replace damaged glass on vehicles. | Review damage reports, prepare or review repair cost estimates, and plan work to be performed. | Sand body areas to be painted and cover bumpers, windows, and trim with masking tape or paper to protect them from the paint. | Soak fiberglass matting in resin mixtures and apply layers of matting over repair areas to specified thicknesses.</t>
+  </si>
+  <si>
+    <t>49-3022.00</t>
+  </si>
+  <si>
+    <t>Automotive Glass Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Automotive Glass Installer (Auto Glass Installer) | Automotive Glass Technician (Auto Glass Technician) | Automotive Glazier (Auto Glazier) | Glass Installer | Glass Installer Technician | Glass Technician | Windshield Installer | Windshield Repair Technician</t>
+  </si>
+  <si>
+    <t>Estimating software | Microsoft Windows | Recordkeeping software | Workday software</t>
+  </si>
+  <si>
+    <t>Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Static Strength | Multilimb Coordination | Manual Dexterity | Speech Recognition | Extent Flexibility | Control Precision | Finger Dexterity | Arm-Hand Steadiness | Visualization | Deductive Reasoning | Problem Sensitivity | Oral Expression | Oral Comprehension | Information Ordering</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Time Pressure | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Outdoors, Under Cover | Exposed to Very Hot or Cold Temperatures | Deal With External Customers or the Public in General | Exposed to Minor Burns, Cuts, Bites, or Stings | Work With or Contribute to a Work Group or Team | Frequency of Decision Making | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Service Technicians and Mechanics | Cleaners of Vehicles and Equipment | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Electric Motor, Power Tool, and Related Repairers | Furniture Finishers | Glass Blowers, Molders, Benders, and Finishers | Glaziers | Grinding and Polishing Workers, Hand | Home Appliance Repairers | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Mechanical Door Repairers | Molders, Shapers, and Casters, Except Metal and Plastic | Painting, Coating, and Decorating Workers | Rail Car Repairers | Structural Metal Fabricators and Fitters | Tire Builders | Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Replace or repair broken windshields and window glass in motor vehicles.</t>
+  </si>
+  <si>
+    <t>Allow all glass parts installed with urethane ample time to cure, taking temperature and humidity into account. | Apply a bead of urethane around the perimeter of each pinchweld and dress the remaining urethane on the pinchwelds so that it is of uniform level and thickness. | Check for and remove moisture or contamination in damaged areas and keep areas dry until repairs are complete. | Cool or warm glass in the event of temperature extremes. | Cut flat safety glass according to specified patterns or perform precision pattern making and glass cutting to custom fit replacement windows. | Hold cut or uneven edges of glass against automated abrasive belts to shape or smooth edges. | Install new foam dams on pinchwelds, if required. | Install replacement glass in vehicles. | Install rubber channeling strips around edges of glass or frames to weatherproof windows or to prevent rattling. | Install, repair, or replace safety glass and related materials, such as back glass heating elements, on vehicles or equipment. | Obtain windshields or windows for specific automobile makes and models from stock and examine them for defects prior to installation. | Prime all scratches on pinchwelds with primer and allow to dry. | Remove all dirt, foreign matter, and loose glass from damaged areas, apply primer along windshield or window edges, and allow primer to dry. | Remove broken or damaged glass windshields or window glass from motor vehicles, using hand tools to remove screws from frames holding glass. | Remove moldings, clips, windshield wipers, screws, bolts, and inside A-pillar moldings and lower headliners in preparation for installation or repair work. | Replace all moldings, clips, windshield wipers, or other parts that were removed prior to glass replacement or repair. | Replace or adjust motorized or manual window-raising mechanisms. | Select appropriate tools, safety equipment, and parts, according to job requirements.</t>
+  </si>
+  <si>
+    <t>49-3023.00</t>
+  </si>
+  <si>
+    <t>Automotive Service Technicians and Mechanics</t>
+  </si>
+  <si>
+    <t>Automotive Drivability Technician (Auto Drivability Tech) | Automotive Mechanic (Auto Mechanic) | Automotive Service Technician (Auto Service Tech) | Automotive Technician (Auto Tech) | Diagnostic Technician (Diagnostic Tech) | Heavy Line Technician (Heavy Line Tech) | Lube Tech (Lubrication Technician) | Mechanic | Quick Service Technician (Quick Service Tech) | Service Technician (Service Tech)</t>
+  </si>
+  <si>
+    <t>Alliance Automotive Shop Controller | Amcom AUTOS2000 | Apple Safari | AutoZone ALLDATA | Blue Streak Electronics Buell Diagnostic | CODA Engine Analysis System | Database software | Estimating software | Genisys Fast Fixes | Hunter WinAlign | IBM Notes | Mainsaver Asset Management | Microsoft Edge | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Mitchell Manager Invoicing System | Mitchell OnDemand5 Manager | Mozilla Firefox | Nexiq Tech HDS Suite for Palm | Online service manual database software | Recordkeeping software | SAP software | SPX/OTC Genisys ConnecTech PC | Scheduling software | Scott Systems MaxxTraxx Pro | Snap-On ShopKey | Technical manual database software | Vehicle management software | Work order management software | YouTube</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Computers and Electronics | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Deductive Reasoning | Manual Dexterity | Near Vision | Finger Dexterity | Problem Sensitivity | Inductive Reasoning | Arm-Hand Steadiness | Control Precision | Extent Flexibility | Visualization | Information Ordering | Oral Comprehension | Written Comprehension | Flexibility of Closure | Perceptual Speed | Selective Attention | Multilimb Coordination | Oral Expression | Time Sharing | Auditory Attention | Visual Color Discrimination | Trunk Strength | Response Orientation | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | In an Enclosed Vehicle or Operate Enclosed Equipment | Frequency of Decision Making | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Time Pressure | Contact With Others | Exposed to Hazardous Conditions | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Exposed to Cramped Work Space, Awkward Positions | Exposed to Hazardous Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Telephone Conversations | Indoors, Not Environmentally Controlled | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Spend Time Bending or Twisting Your Body | Spend Time Making Repetitive Motions | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Engineering Technicians | Automotive Engineers | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electronic Equipment Installers and Repairers, Motor Vehicles | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul automotive vehicles.</t>
+  </si>
+  <si>
+    <t>Align vehicles' front ends. | Align wheels, axles, frames, torsion bars, and steering mechanisms of automobiles, using special alignment equipment and wheel-balancing machines. | Change spark plugs, fuel filters, air filters, and batteries in hybrid electric vehicles. | Conduct visual inspections of compressed natural gas fuel systems to identify cracks, gouges, abrasions, discoloration, broken fibers, loose brackets, damaged gaskets, or other problems. | Confer with customers to obtain descriptions of vehicle problems and to discuss work to be performed and future repair requirements. | Diagnose and replace or repair engine management systems or related sensors for flexible fuel vehicles (FFVs) with ignition timing, fuel rate, alcohol concentration, or air-to-fuel ratio malfunctions. | Disassemble units and inspect parts for wear, using micrometers, calipers, and gauges. | Estimate costs of vehicle repair. | Follow checklists to ensure all important parts are examined, including belts, hoses, steering systems, spark plugs, brake and fuel systems, wheel bearings, and other potentially troublesome areas. | Inspect vehicles for damage and record findings so that necessary repairs can be made. | Install, adjust, or repair hydraulic or electromagnetic automatic lift mechanisms used to raise and lower automobile windows, seats, and tops. | Maintain cleanliness of work area. | Overhaul or replace carburetors, blowers, generators, distributors, starters, and pumps. | Perform routine and scheduled maintenance services, such as oil changes, lubrications, and tune-ups. | Plan work procedures, using charts, technical manuals, and experience. | Rebuild parts, such as crankshafts and cylinder blocks. | Repair and service air conditioning, heating, engine cooling, and electrical systems. | Repair or rebuild transmissions. | Repair or replace parts such as pistons, rods, gears, valves, and bearings. | Repair, reline, replace, and adjust brakes. | Repair, replace, or adjust defective fuel injectors, carburetor parts, and gasoline filters. | Retrofit vehicle fuel systems with aftermarket products, such as vapor transfer devices, evaporation control devices, swirlers, lean burn devices, and friction reduction devices, to enhance combustion and fuel efficiency. | Review work orders and discuss work with supervisors. | Rewire ignition systems, lights, and instrument panels. | Tear down, repair, and rebuild faulty assemblies, such as power systems, steering systems, and linkages. | Test and adjust repaired systems to meet manufacturers' performance specifications. | Test drive vehicles and test components and systems, using equipment such as infrared engine analyzers, compression gauges, and computerized diagnostic devices. | Test electronic computer components in automobiles to ensure proper operation. | Troubleshoot fuel, ignition, and emissions control systems, using electronic testing equipment. | Tune automobile engines to ensure proper and efficient functioning.</t>
+  </si>
+  <si>
+    <t>49-3031.00</t>
+  </si>
+  <si>
+    <t>Bus and Truck Mechanics and Diesel Engine Specialists</t>
+  </si>
+  <si>
+    <t>Bus Mechanic | Diesel Mechanic | Diesel Technician (Diesel Tech) | Fleet Mechanic | General Repair Mechanic | Heavy Truck Mechanic | Service Technician | Trailer Mechanic | Transit Mechanic | Truck Mechanic</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Computerized maintenance management system software CMMS | Cummins INSITE | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Database software | Engine diagnostic software | Fleet management software | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software | Scheduling software | Shop management software</t>
+  </si>
+  <si>
+    <t>Mechanical | Transportation | Education and Training | English Language | Public Safety and Security | Mathematics | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Control Precision | Hearing Sensitivity | Problem Sensitivity | Deductive Reasoning | Multilimb Coordination | Extent Flexibility | Trunk Strength | Information Ordering | Visualization | Flexibility of Closure | Inductive Reasoning | Oral Expression | Oral Comprehension | Auditory Attention | Depth Perception | Speech Recognition | Visual Color Discrimination | Far Vision | Static Strength | Reaction Time | Selective Attention | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Bending or Twisting Your Body | Spend Time Standing | Exposed to Cramped Work Space, Awkward Positions | Impact of Decisions on Co-workers or Company Results | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Contact With Others | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Time Pressure | Spend Time Kneeling, Crouching, Stooping, or Crawling | Work Outcomes and Results of Other Workers | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Farm Equipment Mechanics and Service Technicians | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Ship Engineers | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul buses and trucks, or maintain and repair any type of diesel engines. Includes mechanics working primarily with automobile or marine diesel engines.</t>
+  </si>
+  <si>
+    <t>Adjust and reline brakes, align wheels, tighten bolts and screws, and reassemble equipment. | Adjust or repair computer controlled exhaust emissions devices. | Align front ends and suspension systems. | Attach test instruments to equipment, and read dials and gauges to diagnose malfunctions. | Diagnose and repair vehicle heating and cooling systems. | Disassemble and overhaul internal combustion engines, pumps, generators, transmissions, clutches, and differential units. | Dismount, mount, and repair or replace tires. | Examine and adjust protective guards, loose bolts, and specified safety devices. | Follow green operational practices involving conservation of water or energy or reduction of solid waste. | Inspect and verify dimensions and clearances of parts to ensure conformance to factory specifications. | Inspect brake systems, steering mechanisms, wheel bearings, and other important parts to ensure that they are in proper operating condition. | Inspect, repair, and maintain automotive and mechanical equipment and machinery, such as pumps and compressors. | Inspect, test, and listen to defective equipment to diagnose malfunctions, using test instruments such as handheld computers, motor analyzers, chassis charts, or pressure gauges. | Install or repair accessories. | Maintain or repair vehicles with alternative fuel systems, including biodiesel, hybrid, or compressed natural gas vehicles. | Measure vehicle emissions to determine whether they are within acceptable limits. | Operate valve-grinding machines to grind and reset valves. | Perform routine maintenance such as changing oil, checking batteries, and lubricating equipment and machinery. | Raise trucks, buses, and heavy parts or equipment using hydraulic jacks or hoists. | Rebuild gas or diesel engines. | Recondition and replace parts, pistons, bearings, gears, and valves. | Repair or adjust seats, doors, or windows. | Rewire ignition systems, lights, and instrument panels. | Specialize in repairing and maintaining parts of the engine, such as fuel injection systems. | Test drive trucks and buses to diagnose malfunctions or to ensure that they are working properly. | Use handtools, such as screwdrivers, pliers, wrenches, pressure gauges, or precision instruments, as well as power tools, such as pneumatic wrenches, lathes, welding equipment, or jacks and hoists.</t>
+  </si>
+  <si>
+    <t>49-3041.00</t>
+  </si>
+  <si>
+    <t>Farm Equipment Mechanics and Service Technicians</t>
+  </si>
+  <si>
+    <t>Agricultural Mechanic (Ag Mechanic) | Agricultural Service Technician (Ag Service Tech) | Dairy Service Technician (Dairy Service Tech) | Farm Equipment Mechanic | Farm Equipment Service Technician (Farm Equipment Service Tech) | Field Mechanic | Field Technician (Field Tech) | Mechanic | Service Technician (Service Tech) | Tractor Mechanic</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | FarmLogic FarmPAD | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | ServiceMax | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Monitoring | Active Learning | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | English Language | Computers and Electronics | Engineering and Technology | Physics | Mathematics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Control Precision | Multilimb Coordination | Manual Dexterity | Visualization | Problem Sensitivity | Near Vision | Arm-Hand Steadiness | Deductive Reasoning | Extent Flexibility | Information Ordering | Inductive Reasoning | Hearing Sensitivity | Written Comprehension | Oral Comprehension | Flexibility of Closure | Static Strength | Trunk Strength | Visual Color Discrimination | Auditory Attention | Speech Recognition | Oral Expression | Selective Attention | Speech Clarity | Perceptual Speed | Response Orientation | Speed of Closure | Category Flexibility | Written Expression | Far Vision | Wrist-Finger Speed | Reaction Time | Depth Perception</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Importance of Being Exact or Accurate | Spend Time Standing | Contact With Others | Indoors, Not Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | Exposed to Cramped Work Space, Awkward Positions | Frequency of Decision Making | Exposed to Hazardous Equipment | Time Pressure | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | In an Open Vehicle or Operating Equipment | Health and Safety of Other Workers | Exposed to Very Hot or Cold Temperatures | Determine Tasks, Priorities and Goals | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Deal With External Customers or the Public in General | Spend Time Kneeling, Crouching, Stooping, or Crawling | In an Enclosed Vehicle or Operate Enclosed Equipment</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Boilermakers | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Engine and Other Machine Assemblers | Helpers--Installation, Maintenance, and Repair Workers | Hydroelectric Plant Technicians | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Timing Device Assemblers and Adjusters</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul farm machinery and vehicles, such as tractors, harvesters, dairy equipment, and irrigation systems.</t>
+  </si>
+  <si>
+    <t>Calculate bills according to record of repairs made, labor time, and parts used. | Clean and lubricate parts. | Dismantle defective machines for repair, using hand tools. | Drive trucks to haul tools and equipment for on-site repair of large machinery. | Examine and listen to equipment, read inspection reports, and confer with customers to locate and diagnose malfunctions. | Fabricate new metal parts, using drill presses, engine lathes, and other machine tools. | Install and repair agricultural irrigation, plumbing, and sprinkler systems. | Maintain, repair, and overhaul farm machinery and vehicles, such as tractors, harvesters, and irrigation systems. | Reassemble machines and equipment following repair, testing operation and making adjustments, as necessary. | Record details of repairs made and parts used. | Repair bent or torn sheet metal. | Repair or replace defective parts, using hand tools, milling and woodworking machines, lathes, welding equipment, grinders, or saws. | Test and replace electrical components and wiring, using test meters, soldering equipment, and hand tools. | Tune or overhaul engines.</t>
+  </si>
+  <si>
+    <t>49-3042.00</t>
+  </si>
+  <si>
+    <t>Mobile Heavy Equipment Mechanics, Except Engines</t>
+  </si>
+  <si>
+    <t>Construction Equipment Mechanic | Equipment Mechanic | Equipment Technician | Field Mechanic | Field Service Technician | Field Technician | Heavy Equipment Mechanic | Heavy Equipment Technician | Mechanic | Mobile Heavy Equipment Mechanic</t>
+  </si>
+  <si>
+    <t>Database software | Fleet management software | Maintenance management software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Recordkeeping software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Monitoring | Active Learning | Speaking | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Mathematics | Computers and Electronics | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Control Precision | Finger Dexterity | Extent Flexibility | Near Vision | Problem Sensitivity | Arm-Hand Steadiness | Multilimb Coordination | Visualization | Reaction Time | Information Ordering | Deductive Reasoning | Inductive Reasoning | Flexibility of Closure | Perceptual Speed | Static Strength | Visual Color Discrimination | Far Vision | Trunk Strength | Rate Control | Selective Attention | Category Flexibility | Written Comprehension | Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Auditory Attention | Hearing Sensitivity | Response Orientation</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Frequency of Decision Making | Exposed to Cramped Work Space, Awkward Positions | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Telephone Conversations | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Standing | Exposed to Minor Burns, Cuts, Bites, or Stings | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Spend Time Bending or Twisting Your Body | In an Enclosed Vehicle or Operate Enclosed Equipment | Health and Safety of Other Workers | Time Pressure | E-Mail | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Exposed to Extremely Bright or Inadequate Lighting Conditions | In an Open Vehicle or Operating Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Exposed to Hazardous Conditions | Importance of Repeating Same Tasks | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Whole Body Vibration</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Crane and Tower Operators | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Farm Equipment Mechanics and Service Technicians | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Motorboat Mechanics and Service Technicians | Operating Engineers and Other Construction Equipment Operators | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Riggers</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul mobile mechanical, hydraulic, and pneumatic equipment, such as cranes, bulldozers, graders, and conveyors, used in construction, logging, and mining.</t>
+  </si>
+  <si>
+    <t>Adjust and maintain industrial machinery, using control and regulating devices. | Adjust, maintain, and repair or replace subassemblies, such as transmissions and crawler heads, using hand tools, jacks, and cranes. | Assemble gear systems, and align frames and gears. | Clean parts by spraying them with grease solvent or immersing them in tanks of solvent. | Clean, lubricate, and perform other routine maintenance work on equipment and vehicles. | Diagnose faults or malfunctions to determine required repairs, using engine diagnostic equipment such as computerized test equipment and calibration devices. | Direct workers who are assembling or disassembling equipment or cleaning parts. | Dismantle and reassemble heavy equipment using hoists and hand tools. | Examine parts for damage or excessive wear, using micrometers and gauges. | Fabricate needed parts or items from sheet metal. | Fit bearings to adjust, repair, or overhaul mobile mechanical, hydraulic, and pneumatic equipment. | Operate and inspect machines or heavy equipment to diagnose defects. | Overhaul and test machines or equipment to ensure operating efficiency. | Read and understand operating manuals, blueprints, and technical drawings. | Repair and replace damaged or worn parts. | Repair, rewire, and troubleshoot electrical systems. | Research, order, and maintain parts inventory for services and repairs. | Schedule maintenance for industrial machines and equipment, and keep equipment service records. | Test mechanical products and equipment after repair or assembly to ensure proper performance and compliance with manufacturers' specifications. | Weld or solder broken parts and structural members, using electric or gas welders and soldering tools.</t>
+  </si>
+  <si>
+    <t>49-3043.00</t>
+  </si>
+  <si>
+    <t>Rail Car Repairers</t>
+  </si>
+  <si>
+    <t>Freight Maintenance Specialist | Locomotive Repairman | Rail Car Maintenance Mechanic | Rail Car Mechanic | Rail Car Repairer | Rail Car Repairman | Rail Car Sandblaster | Rail Car Welder | Railroad Car Repairman | Train Car Repairman</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Disassembler software | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mozilla Firefox | RailTech Software Solutions Rail 21 Management System | RailTech Software Systems Mars for the 21st Century | WheelShop Automation.com Wheel Shop Management Suite</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Design | Administration and Management | Building and Construction | Engineering and Technology | Transportation | Mathematics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Control Precision | Multilimb Coordination | Finger Dexterity | Near Vision | Problem Sensitivity | Trunk Strength | Static Strength | Reaction Time | Perceptual Speed | Flexibility of Closure | Extent Flexibility | Far Vision | Visualization | Information Ordering | Deductive Reasoning | Stamina | Selective Attention | Category Flexibility | Inductive Reasoning | Hearing Sensitivity | Visual Color Discrimination | Gross Body Equilibrium | Gross Body Coordination | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Exposed to Extremely Bright or Inadequate Lighting Conditions | Indoors, Not Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Outdoors, Exposed to All Weather Conditions | Freedom to Make Decisions | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Time Pressure | Contact With Others | Exposed to Minor Burns, Cuts, Bites, or Stings | In an Open Vehicle or Operating Equipment | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Physical Proximity | Spend Time Walking or Running | Spend Time Bending or Twisting Your Body | Health and Safety of Other Workers | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to High Places</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Service Technicians and Mechanics | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Helpers--Installation, Maintenance, and Repair Workers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Plumbers, Pipefitters, and Steamfitters | Rail-Track Laying and Maintenance Equipment Operators | Signal and Track Switch Repairers</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul railroad rolling stock, mine cars, or mass transit rail cars.</t>
+  </si>
+  <si>
+    <t>Adjust repaired or replaced units as needed to ensure proper operation. | Align car sides for installation of car ends and crossties, using width gauges, turnbuckles, and wrenches. | Disassemble units such as water pumps, control valves, and compressors so that repairs can be made. | Examine car roofs for wear and damage, and repair defective sections, using roofing material, cement, nails, and waterproof paint. | Inspect components such as bearings, seals, gaskets, wheels, and coupler assemblies to determine if repairs are needed. | Inspect the interior and exterior of rail cars coming into rail yards to identify defects and to determine the extent of wear and damage. | Install and repair interior flooring, fixtures, walls, plumbing, steps, and platforms. | Measure diameters of axle wheel seats, using micrometers, and mark dimensions on axles so that wheels can be bored to specified dimensions. | Paint car exteriors, interiors, and fixtures. | Perform scheduled maintenance, and clean units and components. | Record conditions of cars, and repair and maintenance work performed or to be performed. | Remove locomotives, car mechanical units, or other components, using pneumatic hoists and jacks, pinch bars, hand tools, and cutting torches. | Repair and maintain electrical and electronic controls for propulsion and braking systems. | Repair car upholstery. | Repair or replace defective or worn parts such as bearings, pistons, and gears, using hand tools, torque wrenches, power tools, and welding equipment. | Repair window sash frames, attach weather stripping and channels to frames, and replace window glass, using hand tools. | Repair, fabricate, and install steel or wood fittings, using blueprints, shop sketches, and instruction manuals. | Replace defective wiring and insulation, and tighten electrical connections, using hand tools. | Test electrical systems of cars by operating systems and using testing equipment such as ammeters. | Test units for operability before and after repairs.</t>
+  </si>
+  <si>
+    <t>49-3051.00</t>
+  </si>
+  <si>
+    <t>Motorboat Mechanics and Service Technicians</t>
+  </si>
+  <si>
+    <t>Boat Mechanic | Boat Motor Mechanic | Boat Rigger | Marine Mechanic | Marine Propulsion Technician | Marine Technician | Mechanic | Outboard Motor Mechanic | Outboard Technician | Service Technician</t>
+  </si>
+  <si>
+    <t>CDI Electronics M.E.D.S. | Engine diagnostic scanners | Facebook | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Outboard engine diagnostic software | Rinda Technologies DIACOM Marine</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Computers and Electronics | English Language | Mathematics | Engineering and Technology | Transportation | Administration and Management | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Manual Dexterity | Deductive Reasoning | Inductive Reasoning | Arm-Hand Steadiness | Finger Dexterity | Control Precision | Near Vision | Oral Comprehension | Oral Expression | Information Ordering | Multilimb Coordination | Hearing Sensitivity | Speech Recognition | Extent Flexibility | Trunk Strength | Visualization | Static Strength | Selective Attention | Flexibility of Closure | Category Flexibility | Depth Perception | Far Vision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | In an Open Vehicle or Operating Equipment | Exposed to Contaminants | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Telephone Conversations | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Contact With Others | Spend Time Standing | Time Pressure | Exposed to Cramped Work Space, Awkward Positions | Impact of Decisions on Co-workers or Company Results | Outdoors, Under Cover | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Very Hot or Cold Temperatures | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Exposed to Hazardous Equipment | Work With or Contribute to a Work Group or Team | Exposed to Extremely Bright or Inadequate Lighting Conditions | Consequence of Error | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Engine and Other Machine Assemblers | Farm Equipment Mechanics and Service Technicians | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Marine Engineers and Naval Architects | Mobile Heavy Equipment Mechanics, Except Engines | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Recreational Vehicle Service Technicians | Riggers | Ship Engineers</t>
+  </si>
+  <si>
+    <t>Repair and adjust electrical and mechanical equipment of inboard or inboard-outboard boat engines.</t>
+  </si>
+  <si>
+    <t>Adjust carburetor mixtures, electrical point settings, or timing while motors are running in water-filled test tanks. | Adjust generators and replace faulty wiring, using hand tools and soldering irons. | Disassemble and inspect motors to locate defective parts, using mechanic's hand tools and gauges. | Document inspection and test results and work performed or to be performed. | Idle motors and observe thermometers to determine the effectiveness of cooling systems. | Inspect and repair or adjust propellers or propeller shafts. | Mount motors to boats, and operate boats at various speeds on waterways to conduct operational tests. | Perform routine engine maintenance on motorboats, such as changing oil and filters. | Repair engine mechanical equipment, such as power tilts, bilge pumps, or power take-offs. | Repair or rework parts, using machine tools such as lathes, mills, drills, or grinders. | Replace parts, such as gears, magneto points, piston rings, or spark plugs, and reassemble engines. | Set starter locks and align and repair steering or throttle controls, using gauges, screwdrivers, or wrenches. | Start motors and monitor performance for signs of malfunctioning, such as smoke, excessive vibration, or misfiring.</t>
+  </si>
+  <si>
+    <t>49-3052.00</t>
+  </si>
+  <si>
+    <t>Motorcycle Mechanics</t>
+  </si>
+  <si>
+    <t>All Terrain Vehicle Technician (ATV Technician) | Custom Bike Builder | Motorcycle Mechanic | Motorcycle Service Technician | Motorcycle Technician | Motorsports Technician | Scooter Mechanic | Service Technician</t>
+  </si>
+  <si>
+    <t>AbbottSoft QuickFix | Apple iOS | DealerTrax ShopOrder | Facebook | Inventory tracking software | LightSpeed Cloud | Microsoft Excel | Microsoft Office software | Microsoft Word | Santa Maria Software Counterman Pro | TRACKUM Repair Manager</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Active Learning | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Customer and Personal Service | Computers and Electronics | Mathematics | Education and Training</t>
+  </si>
+  <si>
+    <t>Deductive Reasoning | Inductive Reasoning | Manual Dexterity | Finger Dexterity | Near Vision | Hearing Sensitivity | Oral Comprehension | Arm-Hand Steadiness | Problem Sensitivity | Control Precision | Oral Expression | Auditory Attention | Extent Flexibility | Trunk Strength | Static Strength | Multilimb Coordination | Selective Attention | Visualization | Category Flexibility | Information Ordering | Fluency of Ideas | Speech Clarity | Speech Recognition | Originality | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Frequency of Decision Making | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Contact With Others | Time Pressure | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Bending or Twisting Your Body | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Health and Safety of Other Workers | Spend Time Making Repetitive Motions | Exposed to Cramped Work Space, Awkward Positions | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Walking or Running | Exposed to Very Hot or Cold Temperatures | In an Open Vehicle or Operating Equipment | Importance of Repeating Same Tasks | Spend Time Kneeling, Crouching, Stooping, or Crawling | Indoors, Environmentally Controlled | E-Mail | Level of Competition | Written Letters and Memos | Deal With External Customers or the Public in General | Exposed to Hazardous Equipment | Dealing With Unpleasant, Angry, or Discourteous People | Outdoors, Exposed to All Weather Conditions</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Service Technicians and Mechanics | Avionics Technicians | Bicycle Repairers | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electronic Equipment Installers and Repairers, Motor Vehicles | Engine and Other Machine Assemblers | Farm Equipment Mechanics and Service Technicians | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Recreational Vehicle Service Technicians | Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul motorcycles, scooters, mopeds, dirt bikes, or similar motorized vehicles.</t>
+  </si>
+  <si>
+    <t>Connect test panels to engines and measure generator output, ignition timing, or other engine performance indicators. | Disassemble subassembly units and examine condition, movement, or alignment of parts, visually or using gauges. | Dismantle engines and repair or replace defective parts, such as magnetos, carburetors, or generators. | Hammer out dents and bends in frames and weld tears and breaks. | Install motorcycle accessories. | Listen to engines, examine vehicle frames, or confer with customers to determine nature and extent of malfunction or damage. | Mount, balance, change, or check condition or pressure of tires. | Reassemble and test subassembly units. | Reassemble frames and reinstall engines after repairs. | Remove cylinder heads and grind valves to scrape off carbon and replace defective valves, pistons, cylinders, or rings, using hand and power tools. | Repair or adjust motorcycle subassemblies, such as forks, transmissions, brakes, or drive chains, according to specifications. | Repair or replace other parts, such as headlights, horns, handlebar controls, gasoline or oil tanks, starters, or mufflers. | Replace defective parts, using hand tools, arbor presses, flexible power presses, or power tools.</t>
+  </si>
+  <si>
+    <t>49-3053.00</t>
+  </si>
+  <si>
+    <t>Outdoor Power Equipment and Other Small Engine Mechanics</t>
+  </si>
+  <si>
+    <t>Chainsaw Technician | Golf Cart Mechanic | Lawnmower Repair Mechanic | Mechanic | Outdoor Power Equipment Service Technician | Service Technician (Service Tech) | Shop Mechanic | Small Engine Mechanic | Small Engine Technician (Small Engine Tech)</t>
+  </si>
+  <si>
+    <t>Ideal Computer Systems Ideal OPE | Land &amp; Sea DYNO-MAX | Microsoft Excel | Microsoft Office software | RepairTRAX | Sale processing software | Smart Equipment Repair | VersaDyne small engine test system | Web browser software</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | English Language | Engineering and Technology | Education and Training | Transportation | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Near Vision | Control Precision | Visualization | Information Ordering | Problem Sensitivity | Deductive Reasoning | Extent Flexibility | Multilimb Coordination | Oral Comprehension | Oral Expression | Selective Attention | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Auditory Attention | Hearing Sensitivity | Static Strength</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | In an Open Vehicle or Operating Equipment | Telephone Conversations | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Outdoors, Exposed to All Weather Conditions | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Bicycle Repairers | Bus and Truck Mechanics and Diesel Engine Specialists | Cleaners of Vehicles and Equipment | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Farm Equipment Mechanics and Service Technicians | Home Appliance Repairers | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Rail Car Repairers | Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Diagnose, adjust, repair, or overhaul small engines used to power lawn mowers, chain saws, recreational sporting equipment, and related equipment.</t>
+  </si>
+  <si>
+    <t>Adjust points, valves, carburetors, distributors, and spark plug gaps, using feeler gauges. | Dismantle engines, using hand tools, and examine parts for defects. | Grind, ream, rebore, and re-tap parts to obtain specified clearances, using grinders, lathes, taps, reamers, boring machines, and micrometers. | Obtain problem descriptions from customers, and prepare cost estimates for repairs. | Perform routine maintenance such as cleaning and oiling parts, honing cylinders, and tuning ignition systems. | Reassemble engines after repair or maintenance work is complete. | Record repairs made, time spent, and parts used. | Remove engines from equipment, and position and bolt engines to repair stands. | Repair and maintain gasoline engines used to power equipment such as portable saws, lawn mowers, generators, and compressors. | Repair or replace defective parts such as magnetos, water pumps, gears, pistons, and carburetors, using hand tools. | Replace motors. | Sell parts and equipment. | Show customers how to maintain equipment. | Test and inspect engines to determine malfunctions, to locate missing and broken parts, and to verify repairs, using diagnostic instruments.</t>
+  </si>
+  <si>
+    <t>49-3091.00</t>
+  </si>
+  <si>
+    <t>Bicycle Repairers</t>
+  </si>
+  <si>
+    <t>Bicycle Fitter | Bicycle Mechanic | Bicycle Repair Technician | Bicycle Repairman | Bicycle Service Technician | Bicycle Technician | Bike Mechanic</t>
+  </si>
+  <si>
+    <t>LightSpeed Cloud | Microsoft Excel | Microsoft Outlook | Microsoft Word | Pedal Powered Software Bicycle Repair Man | RepairTRAX | Upland Consulting Group Repair Traq | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Sales and Marketing | English Language | Engineering and Technology | Administration and Management | Design | Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Visualization | Finger Dexterity | Near Vision | Arm-Hand Steadiness | Manual Dexterity | Information Ordering | Problem Sensitivity | Oral Expression | Speech Clarity | Oral Comprehension | Speech Recognition | Control Precision | Written Comprehension | Extent Flexibility | Selective Attention | Category Flexibility | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Indoors, Environmentally Controlled | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Time Pressure | Spend Time Standing | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | E-Mail | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Spend Time Making Repetitive Motions | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Service Technicians and Mechanics | Bus and Truck Mechanics and Diesel Engine Specialists | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Farm Equipment Mechanics and Service Technicians | Helpers--Installation, Maintenance, and Repair Workers | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Recreational Vehicle Service Technicians | Riggers | Shoe and Leather Workers and Repairers | Tire Builders | Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Repair and service bicycles.</t>
+  </si>
+  <si>
+    <t>Align wheels. | Assemble new bicycles. | Build wheels by cutting and threading new spokes. | Clean and lubricate bicycle parts. | Disassemble axles to repair, adjust, and replace defective parts, using hand tools. | Help customers select bicycles that fit their body sizes and intended bicycle uses. | Install and adjust brakes and brake pads. | Install and adjust speed and gear mechanisms. | Install new tires and tubes. | Install, repair, and replace equipment or accessories, such as handlebars, stands, lights, and seats. | Order bicycle parts. | Repair holes in tire tubes, using scrapers and patches. | Sell bicycles and accessories. | Shape replacement parts, using bench grinders.</t>
+  </si>
+  <si>
+    <t>49-3092.00</t>
+  </si>
+  <si>
+    <t>Recreational Vehicle Service Technicians</t>
+  </si>
+  <si>
+    <t>ATV Tech (All-Terrain Vehicle Technician) | Certified RV Technician (Certified Recreational Vehicle Technician) | Hitch Technician (Hitch Tech) | Mobile Service RV Technician (Mobile Service Recreational Vehicle Technician) | RV Body Mechanic (Recreational Vehicle Body Mechanic) | RV Mechanic (Recreational Vehicle Mechanic) | RV Service Technician (Recreational Vehicle Service Technician) | RV Tech (Recreational Vehicle Technician) | RVDA Master Certified RV Technician (Recreational Vehicle Dealer Association Master Certified Recreational Vehicle Technician) | Service Technician (Service Tech)</t>
+  </si>
+  <si>
+    <t>Email software | Facebook | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Word | RV Damage Repair Estimator | Summit Ordering Systems RvInvoiceWriter | Topline Software Solutions Topline Service Manager</t>
+  </si>
+  <si>
+    <t>Active Learning | Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Customer and Personal Service | Administration and Management | Education and Training | English Language | Engineering and Technology | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Problem Sensitivity | Oral Expression | Finger Dexterity | Control Precision | Oral Comprehension | Speech Clarity | Arm-Hand Steadiness | Information Ordering | Deductive Reasoning | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Written Comprehension | Speech Recognition | Extent Flexibility | Trunk Strength | Multilimb Coordination | Visualization | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Indoors, Not Environmentally Controlled | Spend Time Standing | Freedom to Make Decisions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Frequency of Decision Making | Contact With Others | Outdoors, Exposed to All Weather Conditions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Minor Burns, Cuts, Bites, or Stings | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | In an Enclosed Vehicle or Operate Enclosed Equipment | Impact of Decisions on Co-workers or Company Results | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Body and Related Repairers | Automotive Service Technicians and Mechanics | Bicycle Repairers | Bus and Truck Mechanics and Diesel Engine Specialists | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electronic Equipment Installers and Repairers, Motor Vehicles | Elevator and Escalator Installers and Repairers | Engine and Other Machine Assemblers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Installation, Maintenance, and Repair Workers | Home Appliance Repairers | Maintenance and Repair Workers, General | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Plumbers, Pipefitters, and Steamfitters | Rail Car Repairers</t>
+  </si>
+  <si>
+    <t>Diagnose, inspect, adjust, repair, or overhaul recreational vehicles including travel trailers. May specialize in maintaining gas, electrical, hydraulic, plumbing, or chassis/towing systems as well as repairing generators, appliances, and interior components. Includes workers who perform customized van conversions.</t>
+  </si>
+  <si>
+    <t>Confer with customers, read work orders, or examine vehicles needing repair to determine the nature and extent of damage. | Connect electrical systems to outside power sources, and activate switches to test the operation of appliances or light fixtures. | Connect water hoses to inlet pipes of plumbing systems, and test operation of toilets or sinks. | Diagnose and repair furnace or air conditioning systems. | Examine or test operation of parts or systems to ensure completeness of repairs. | Explain proper operation of vehicle systems to customers. | Inspect recreational vehicles to diagnose problems and perform necessary adjustment, repair, or overhaul. | Inspect, repair, or replace brake systems. | List parts needed, estimate costs, and plan work procedures, using parts lists, technical manuals, or diagrams. | Locate and repair frayed wiring, broken connections, or incorrect wiring, using ohmmeters, soldering irons, tape, or hand tools. | Open and close doors, windows, or drawers to test their operation, trimming edges to fit, as necessary. | Refinish wood surfaces on cabinets, doors, moldings, or floors, using power sanders, putty, spray equipment, brushes, paints, or varnishes. | Remove damaged exterior panels, and repair and replace structural frame members. | Repair leaks with caulking compound or replace pipes, using pipe wrenches. | Repair plumbing or propane gas lines, using caulking compounds and plastic or copper pipe. | Reset hardware, using chisels, mallets, and screwdrivers. | Seal open sides of modular units to prepare them for shipment, using polyethylene sheets, nails, and hammers.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1958,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" t="s">
+        <v>183</v>
+      </c>
+      <c r="J17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18" t="s">
+        <v>191</v>
+      </c>
+      <c r="H18" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" t="s">
+        <v>200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>201</v>
+      </c>
+      <c r="G19" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" t="s">
+        <v>203</v>
+      </c>
+      <c r="I19" t="s">
+        <v>204</v>
+      </c>
+      <c r="J19" t="s">
+        <v>205</v>
+      </c>
+      <c r="K19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" t="s">
+        <v>216</v>
+      </c>
+      <c r="K20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" t="s">
+        <v>223</v>
+      </c>
+      <c r="I21" t="s">
+        <v>224</v>
+      </c>
+      <c r="J21" t="s">
+        <v>225</v>
+      </c>
+      <c r="K21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" t="s">
+        <v>233</v>
+      </c>
+      <c r="H22" t="s">
+        <v>234</v>
+      </c>
+      <c r="I22" t="s">
+        <v>235</v>
+      </c>
+      <c r="J22" t="s">
+        <v>236</v>
+      </c>
+      <c r="K22" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" t="s">
+        <v>242</v>
+      </c>
+      <c r="F23" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" t="s">
+        <v>244</v>
+      </c>
+      <c r="H23" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" t="s">
+        <v>246</v>
+      </c>
+      <c r="J23" t="s">
+        <v>247</v>
+      </c>
+      <c r="K23" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24" t="s">
+        <v>253</v>
+      </c>
+      <c r="F24" t="s">
+        <v>254</v>
+      </c>
+      <c r="G24" t="s">
+        <v>255</v>
+      </c>
+      <c r="H24" t="s">
+        <v>256</v>
+      </c>
+      <c r="I24" t="s">
+        <v>257</v>
+      </c>
+      <c r="J24" t="s">
+        <v>258</v>
+      </c>
+      <c r="K24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" t="s">
+        <v>263</v>
+      </c>
+      <c r="G25" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" t="s">
+        <v>265</v>
+      </c>
+      <c r="J25" t="s">
+        <v>266</v>
+      </c>
+      <c r="K25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" t="s">
+        <v>272</v>
+      </c>
+      <c r="F26" t="s">
+        <v>273</v>
+      </c>
+      <c r="G26" t="s">
+        <v>274</v>
+      </c>
+      <c r="H26" t="s">
+        <v>275</v>
+      </c>
+      <c r="I26" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" t="s">
+        <v>277</v>
+      </c>
+      <c r="K26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" t="s">
+        <v>284</v>
+      </c>
+      <c r="G27" t="s">
+        <v>285</v>
+      </c>
+      <c r="H27" t="s">
+        <v>286</v>
+      </c>
+      <c r="I27" t="s">
+        <v>287</v>
+      </c>
+      <c r="J27" t="s">
+        <v>288</v>
+      </c>
+      <c r="K27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" t="s">
+        <v>293</v>
+      </c>
+      <c r="E28" t="s">
+        <v>294</v>
+      </c>
+      <c r="F28" t="s">
+        <v>295</v>
+      </c>
+      <c r="G28" t="s">
+        <v>296</v>
+      </c>
+      <c r="H28" t="s">
+        <v>297</v>
+      </c>
+      <c r="I28" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" t="s">
+        <v>299</v>
+      </c>
+      <c r="K28" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B29" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" t="s">
+        <v>304</v>
+      </c>
+      <c r="E29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F29" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" t="s">
+        <v>307</v>
+      </c>
+      <c r="H29" t="s">
+        <v>308</v>
+      </c>
+      <c r="I29" t="s">
+        <v>309</v>
+      </c>
+      <c r="J29" t="s">
+        <v>310</v>
+      </c>
+      <c r="K29" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" t="s">
+        <v>315</v>
+      </c>
+      <c r="E30" t="s">
+        <v>316</v>
+      </c>
+      <c r="F30" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" t="s">
+        <v>319</v>
+      </c>
+      <c r="I30" t="s">
+        <v>320</v>
+      </c>
+      <c r="J30" t="s">
+        <v>321</v>
+      </c>
+      <c r="K30" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" t="s">
+        <v>326</v>
+      </c>
+      <c r="E31" t="s">
+        <v>327</v>
+      </c>
+      <c r="F31" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" t="s">
+        <v>329</v>
+      </c>
+      <c r="H31" t="s">
+        <v>330</v>
+      </c>
+      <c r="I31" t="s">
+        <v>331</v>
+      </c>
+      <c r="J31" t="s">
+        <v>332</v>
+      </c>
+      <c r="K31" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" t="s">
+        <v>335</v>
+      </c>
+      <c r="C32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" t="s">
+        <v>338</v>
+      </c>
+      <c r="F32" t="s">
+        <v>339</v>
+      </c>
+      <c r="G32" t="s">
+        <v>340</v>
+      </c>
+      <c r="H32" t="s">
+        <v>341</v>
+      </c>
+      <c r="I32" t="s">
+        <v>342</v>
+      </c>
+      <c r="J32" t="s">
+        <v>343</v>
+      </c>
+      <c r="K32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>345</v>
+      </c>
+      <c r="B33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D33" t="s">
+        <v>348</v>
+      </c>
+      <c r="E33" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G33" t="s">
+        <v>351</v>
+      </c>
+      <c r="H33" t="s">
+        <v>352</v>
+      </c>
+      <c r="I33" t="s">
+        <v>353</v>
+      </c>
+      <c r="J33" t="s">
+        <v>354</v>
+      </c>
+      <c r="K33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B34" t="s">
+        <v>357</v>
+      </c>
+      <c r="C34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D34" t="s">
+        <v>359</v>
+      </c>
+      <c r="E34" t="s">
+        <v>360</v>
+      </c>
+      <c r="F34" t="s">
+        <v>361</v>
+      </c>
+      <c r="G34" t="s">
+        <v>362</v>
+      </c>
+      <c r="H34" t="s">
+        <v>363</v>
+      </c>
+      <c r="I34" t="s">
+        <v>364</v>
+      </c>
+      <c r="J34" t="s">
+        <v>365</v>
+      </c>
+      <c r="K34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>367</v>
+      </c>
+      <c r="B35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" t="s">
+        <v>369</v>
+      </c>
+      <c r="D35" t="s">
+        <v>370</v>
+      </c>
+      <c r="E35" t="s">
+        <v>371</v>
+      </c>
+      <c r="F35" t="s">
+        <v>372</v>
+      </c>
+      <c r="G35" t="s">
+        <v>373</v>
+      </c>
+      <c r="H35" t="s">
+        <v>374</v>
+      </c>
+      <c r="I35" t="s">
+        <v>375</v>
+      </c>
+      <c r="J35" t="s">
+        <v>376</v>
+      </c>
+      <c r="K35" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>378</v>
+      </c>
+      <c r="B36" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" t="s">
+        <v>380</v>
+      </c>
+      <c r="D36" t="s">
+        <v>381</v>
+      </c>
+      <c r="E36" t="s">
+        <v>382</v>
+      </c>
+      <c r="F36" t="s">
+        <v>383</v>
+      </c>
+      <c r="G36" t="s">
+        <v>384</v>
+      </c>
+      <c r="H36" t="s">
+        <v>385</v>
+      </c>
+      <c r="I36" t="s">
+        <v>386</v>
+      </c>
+      <c r="J36" t="s">
+        <v>387</v>
+      </c>
+      <c r="K36" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>389</v>
+      </c>
+      <c r="B37" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" t="s">
+        <v>391</v>
+      </c>
+      <c r="D37" t="s">
+        <v>392</v>
+      </c>
+      <c r="E37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F37" t="s">
+        <v>394</v>
+      </c>
+      <c r="G37" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" t="s">
+        <v>396</v>
+      </c>
+      <c r="I37" t="s">
+        <v>397</v>
+      </c>
+      <c r="J37" t="s">
+        <v>398</v>
+      </c>
+      <c r="K37" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>400</v>
+      </c>
+      <c r="B38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C38" t="s">
+        <v>402</v>
+      </c>
+      <c r="D38" t="s">
+        <v>403</v>
+      </c>
+      <c r="E38" t="s">
+        <v>404</v>
+      </c>
+      <c r="F38" t="s">
+        <v>405</v>
+      </c>
+      <c r="G38" t="s">
+        <v>406</v>
+      </c>
+      <c r="H38" t="s">
+        <v>407</v>
+      </c>
+      <c r="I38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J38" t="s">
+        <v>409</v>
+      </c>
+      <c r="K38" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>411</v>
+      </c>
+      <c r="B39" t="s">
+        <v>412</v>
+      </c>
+      <c r="C39" t="s">
+        <v>413</v>
+      </c>
+      <c r="D39" t="s">
+        <v>414</v>
+      </c>
+      <c r="E39" t="s">
+        <v>415</v>
+      </c>
+      <c r="F39" t="s">
+        <v>416</v>
+      </c>
+      <c r="G39" t="s">
+        <v>417</v>
+      </c>
+      <c r="H39" t="s">
+        <v>418</v>
+      </c>
+      <c r="I39" t="s">
+        <v>419</v>
+      </c>
+      <c r="J39" t="s">
+        <v>420</v>
+      </c>
+      <c r="K39" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>422</v>
+      </c>
+      <c r="B40" t="s">
+        <v>423</v>
+      </c>
+      <c r="C40" t="s">
+        <v>424</v>
+      </c>
+      <c r="D40" t="s">
+        <v>425</v>
+      </c>
+      <c r="E40" t="s">
+        <v>426</v>
+      </c>
+      <c r="F40" t="s">
+        <v>427</v>
+      </c>
+      <c r="G40" t="s">
+        <v>428</v>
+      </c>
+      <c r="H40" t="s">
+        <v>429</v>
+      </c>
+      <c r="I40" t="s">
+        <v>430</v>
+      </c>
+      <c r="J40" t="s">
+        <v>431</v>
+      </c>
+      <c r="K40" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>433</v>
+      </c>
+      <c r="B41" t="s">
+        <v>434</v>
+      </c>
+      <c r="C41" t="s">
+        <v>435</v>
+      </c>
+      <c r="D41" t="s">
+        <v>436</v>
+      </c>
+      <c r="E41" t="s">
+        <v>200</v>
+      </c>
+      <c r="F41" t="s">
+        <v>437</v>
+      </c>
+      <c r="G41" t="s">
+        <v>438</v>
+      </c>
+      <c r="H41" t="s">
+        <v>439</v>
+      </c>
+      <c r="I41" t="s">
+        <v>440</v>
+      </c>
+      <c r="J41" t="s">
+        <v>441</v>
+      </c>
+      <c r="K41" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>443</v>
+      </c>
+      <c r="B42" t="s">
+        <v>444</v>
+      </c>
+      <c r="C42" t="s">
+        <v>445</v>
+      </c>
+      <c r="D42" t="s">
+        <v>446</v>
+      </c>
+      <c r="E42" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" t="s">
+        <v>447</v>
+      </c>
+      <c r="G42" t="s">
+        <v>448</v>
+      </c>
+      <c r="H42" t="s">
+        <v>449</v>
+      </c>
+      <c r="I42" t="s">
+        <v>450</v>
+      </c>
+      <c r="J42" t="s">
+        <v>451</v>
+      </c>
+      <c r="K42" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" t="s">
+        <v>454</v>
+      </c>
+      <c r="C43" t="s">
+        <v>455</v>
+      </c>
+      <c r="D43" t="s">
+        <v>456</v>
+      </c>
+      <c r="E43" t="s">
+        <v>457</v>
+      </c>
+      <c r="F43" t="s">
+        <v>458</v>
+      </c>
+      <c r="G43" t="s">
+        <v>459</v>
+      </c>
+      <c r="H43" t="s">
+        <v>460</v>
+      </c>
+      <c r="I43" t="s">
+        <v>461</v>
+      </c>
+      <c r="J43" t="s">
+        <v>462</v>
+      </c>
+      <c r="K43" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>464</v>
+      </c>
+      <c r="B44" t="s">
+        <v>465</v>
+      </c>
+      <c r="C44" t="s">
+        <v>466</v>
+      </c>
+      <c r="D44" t="s">
+        <v>467</v>
+      </c>
+      <c r="E44" t="s">
+        <v>468</v>
+      </c>
+      <c r="F44" t="s">
+        <v>469</v>
+      </c>
+      <c r="G44" t="s">
+        <v>470</v>
+      </c>
+      <c r="H44" t="s">
+        <v>471</v>
+      </c>
+      <c r="I44" t="s">
+        <v>472</v>
+      </c>
+      <c r="J44" t="s">
+        <v>473</v>
+      </c>
+      <c r="K44" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>475</v>
+      </c>
+      <c r="B45" t="s">
+        <v>476</v>
+      </c>
+      <c r="C45" t="s">
+        <v>477</v>
+      </c>
+      <c r="D45" t="s">
+        <v>478</v>
+      </c>
+      <c r="E45" t="s">
+        <v>479</v>
+      </c>
+      <c r="F45" t="s">
+        <v>480</v>
+      </c>
+      <c r="G45" t="s">
+        <v>481</v>
+      </c>
+      <c r="H45" t="s">
+        <v>482</v>
+      </c>
+      <c r="I45" t="s">
+        <v>483</v>
+      </c>
+      <c r="J45" t="s">
+        <v>484</v>
+      </c>
+      <c r="K45" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>486</v>
+      </c>
+      <c r="B46" t="s">
+        <v>487</v>
+      </c>
+      <c r="C46" t="s">
+        <v>488</v>
+      </c>
+      <c r="D46" t="s">
+        <v>489</v>
+      </c>
+      <c r="E46" t="s">
+        <v>479</v>
+      </c>
+      <c r="F46" t="s">
+        <v>490</v>
+      </c>
+      <c r="G46" t="s">
+        <v>491</v>
+      </c>
+      <c r="H46" t="s">
+        <v>492</v>
+      </c>
+      <c r="I46" t="s">
+        <v>493</v>
+      </c>
+      <c r="J46" t="s">
+        <v>494</v>
+      </c>
+      <c r="K46" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" t="s">
+        <v>497</v>
+      </c>
+      <c r="C47" t="s">
+        <v>498</v>
+      </c>
+      <c r="D47" t="s">
+        <v>499</v>
+      </c>
+      <c r="E47" t="s">
+        <v>500</v>
+      </c>
+      <c r="F47" t="s">
+        <v>501</v>
+      </c>
+      <c r="G47" t="s">
+        <v>502</v>
+      </c>
+      <c r="H47" t="s">
+        <v>503</v>
+      </c>
+      <c r="I47" t="s">
+        <v>504</v>
+      </c>
+      <c r="J47" t="s">
+        <v>505</v>
+      </c>
+      <c r="K47" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>507</v>
+      </c>
+      <c r="B48" t="s">
+        <v>508</v>
+      </c>
+      <c r="C48" t="s">
+        <v>509</v>
+      </c>
+      <c r="D48" t="s">
+        <v>510</v>
+      </c>
+      <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" t="s">
+        <v>511</v>
+      </c>
+      <c r="G48" t="s">
+        <v>512</v>
+      </c>
+      <c r="H48" t="s">
+        <v>513</v>
+      </c>
+      <c r="I48" t="s">
+        <v>514</v>
+      </c>
+      <c r="J48" t="s">
+        <v>515</v>
+      </c>
+      <c r="K48" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>517</v>
+      </c>
+      <c r="B49" t="s">
+        <v>518</v>
+      </c>
+      <c r="C49" t="s">
+        <v>519</v>
+      </c>
+      <c r="D49" t="s">
+        <v>520</v>
+      </c>
+      <c r="E49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F49" t="s">
+        <v>522</v>
+      </c>
+      <c r="G49" t="s">
+        <v>523</v>
+      </c>
+      <c r="H49" t="s">
+        <v>524</v>
+      </c>
+      <c r="I49" t="s">
+        <v>525</v>
+      </c>
+      <c r="J49" t="s">
+        <v>526</v>
+      </c>
+      <c r="K49" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>528</v>
+      </c>
+      <c r="B50" t="s">
+        <v>529</v>
+      </c>
+      <c r="C50" t="s">
+        <v>530</v>
+      </c>
+      <c r="D50" t="s">
+        <v>531</v>
+      </c>
+      <c r="E50" t="s">
+        <v>532</v>
+      </c>
+      <c r="F50" t="s">
+        <v>533</v>
+      </c>
+      <c r="G50" t="s">
+        <v>534</v>
+      </c>
+      <c r="H50" t="s">
+        <v>535</v>
+      </c>
+      <c r="I50" t="s">
+        <v>536</v>
+      </c>
+      <c r="J50" t="s">
+        <v>537</v>
+      </c>
+      <c r="K50" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>